--- a/data/20251212-OdonTraits_Europe.xlsx
+++ b/data/20251212-OdonTraits_Europe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Mijn Drive\PRJ_Odonata_global\OdonTraits Europe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\te19xejy\Documents\local projects\odontraitseurope\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2C1DF714-9309-49A1-8511-25E9E2C602E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0F9A82-B8C8-4CE3-982F-A1B756BE880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="taxonomic" sheetId="2" r:id="rId1"/>
@@ -43,8 +43,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1938,9 +1936,6 @@
     <t>B2ab(iii)</t>
   </si>
   <si>
-    <t>sheet</t>
-  </si>
-  <si>
     <t>Column_label</t>
   </si>
   <si>
@@ -1950,9 +1945,6 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>imago</t>
-  </si>
-  <si>
     <t>minimal adult body size in millimeters</t>
   </si>
   <si>
@@ -1983,9 +1975,6 @@
     <t>expert opinion De  Knijf</t>
   </si>
   <si>
-    <t>larvae_exuvia</t>
-  </si>
-  <si>
     <t>minimal exuvia total length in millimeters (including caudal lamellae for Zygoptera)</t>
   </si>
   <si>
@@ -2007,9 +1996,6 @@
     <t>maximal exuvia length of caudal lamellae (mm) for Zygoptera only</t>
   </si>
   <si>
-    <t>ecological</t>
-  </si>
-  <si>
     <t>habitat preference: 1 - eutrophic; 2 - oligotrophic; 3 - temporary waters; 4 - streams and rivers; 5 - southern streams and rivers (= Mediterranean); 6 - generalist (species occurring in a wide range of standing and flowing waters)</t>
   </si>
   <si>
@@ -2068,9 +2054,6 @@
   </si>
   <si>
     <t>expert opinion, Brochard &amp; De Knijf</t>
-  </si>
-  <si>
-    <t>protection_endemism</t>
   </si>
   <si>
     <t xml:space="preserve">Species listed in the Council of Europe’s Convention on the Conservation of European Wildlife and Natural Habitats (1979), or Bern Convention, which was the first legal convention to protect Europe’s wild plants and animals. </t>
@@ -2110,9 +2093,6 @@
     <t>Species just occurs marginally outside Europe, i.e. North Africa, Turkey or just east of the Ural Mountains</t>
   </si>
   <si>
-    <t>conservation</t>
-  </si>
-  <si>
     <t>Red List category in Europe as assessed in the European Red List of 2024: Critically Endangered (CR); Endangered (EN); Vulnerable (VU); Near Threatened (NT); Data Deficient (DD); Least Concern (LC); Not Applicable (NA) (species does not occur in the focal region)</t>
   </si>
   <si>
@@ -2210,12 +2190,30 @@
   <si>
     <t>personal communication C. Diaz</t>
   </si>
+  <si>
+    <t>imago.csv</t>
+  </si>
+  <si>
+    <t>File</t>
+  </si>
+  <si>
+    <t>larvae_exuvia.csv</t>
+  </si>
+  <si>
+    <t>ecological.csv</t>
+  </si>
+  <si>
+    <t>protection_endemism.csv</t>
+  </si>
+  <si>
+    <t>conservation.csv</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2478,8 +2476,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="29">
     <dxf>
@@ -2728,9 +2726,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2768,9 +2766,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2803,9 +2801,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2838,9 +2853,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3015,7 +3047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E144"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="48.42578125" bestFit="1" customWidth="1"/>
@@ -3024,7 +3056,7 @@
     <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -3041,7 +3073,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3058,7 +3090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -3075,7 +3107,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -3092,7 +3124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -3109,7 +3141,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -3126,7 +3158,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -3143,7 +3175,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -3160,7 +3192,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -3177,7 +3209,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -3194,7 +3226,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -3211,7 +3243,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -3228,7 +3260,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -3245,7 +3277,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -3262,7 +3294,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -3279,7 +3311,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3296,7 +3328,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -3313,7 +3345,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -3330,7 +3362,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
@@ -3347,7 +3379,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
@@ -3364,7 +3396,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -3381,7 +3413,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -3398,7 +3430,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>76</v>
       </c>
@@ -3415,7 +3447,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>79</v>
       </c>
@@ -3432,7 +3464,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>82</v>
       </c>
@@ -3449,7 +3481,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>87</v>
       </c>
@@ -3466,7 +3498,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>90</v>
       </c>
@@ -3483,7 +3515,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -3500,7 +3532,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>97</v>
       </c>
@@ -3517,7 +3549,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>100</v>
       </c>
@@ -3534,7 +3566,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
@@ -3551,7 +3583,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>106</v>
       </c>
@@ -3568,7 +3600,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>109</v>
       </c>
@@ -3585,7 +3617,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>112</v>
       </c>
@@ -3602,7 +3634,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>115</v>
       </c>
@@ -3619,7 +3651,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>118</v>
       </c>
@@ -3636,7 +3668,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>121</v>
       </c>
@@ -3653,7 +3685,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>124</v>
       </c>
@@ -3670,7 +3702,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>127</v>
       </c>
@@ -3687,7 +3719,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>130</v>
       </c>
@@ -3704,7 +3736,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>133</v>
       </c>
@@ -3721,7 +3753,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>136</v>
       </c>
@@ -3738,7 +3770,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>140</v>
       </c>
@@ -3755,7 +3787,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>144</v>
       </c>
@@ -3772,7 +3804,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>147</v>
       </c>
@@ -3789,7 +3821,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>150</v>
       </c>
@@ -3806,7 +3838,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>154</v>
       </c>
@@ -3823,7 +3855,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>157</v>
       </c>
@@ -3840,7 +3872,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>160</v>
       </c>
@@ -3857,7 +3889,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>163</v>
       </c>
@@ -3874,7 +3906,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>166</v>
       </c>
@@ -3891,7 +3923,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>169</v>
       </c>
@@ -3908,7 +3940,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>172</v>
       </c>
@@ -3925,7 +3957,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>175</v>
       </c>
@@ -3942,7 +3974,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>178</v>
       </c>
@@ -3959,7 +3991,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>181</v>
       </c>
@@ -3976,7 +4008,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>185</v>
       </c>
@@ -3993,7 +4025,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>189</v>
       </c>
@@ -4010,7 +4042,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>192</v>
       </c>
@@ -4027,7 +4059,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>197</v>
       </c>
@@ -4044,7 +4076,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>200</v>
       </c>
@@ -4061,7 +4093,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>203</v>
       </c>
@@ -4078,7 +4110,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>206</v>
       </c>
@@ -4095,7 +4127,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>209</v>
       </c>
@@ -4112,7 +4144,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>212</v>
       </c>
@@ -4129,7 +4161,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>215</v>
       </c>
@@ -4146,7 +4178,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>220</v>
       </c>
@@ -4163,7 +4195,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>224</v>
       </c>
@@ -4180,7 +4212,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>228</v>
       </c>
@@ -4197,7 +4229,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>231</v>
       </c>
@@ -4214,7 +4246,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>234</v>
       </c>
@@ -4231,7 +4263,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>237</v>
       </c>
@@ -4248,7 +4280,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>240</v>
       </c>
@@ -4265,7 +4297,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>243</v>
       </c>
@@ -4282,7 +4314,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>246</v>
       </c>
@@ -4299,7 +4331,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>249</v>
       </c>
@@ -4316,7 +4348,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>254</v>
       </c>
@@ -4333,7 +4365,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>259</v>
       </c>
@@ -4350,7 +4382,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>262</v>
       </c>
@@ -4367,7 +4399,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>265</v>
       </c>
@@ -4384,7 +4416,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>268</v>
       </c>
@@ -4401,7 +4433,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>271</v>
       </c>
@@ -4418,7 +4450,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>275</v>
       </c>
@@ -4435,7 +4467,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>279</v>
       </c>
@@ -4452,7 +4484,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>282</v>
       </c>
@@ -4469,7 +4501,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>285</v>
       </c>
@@ -4486,7 +4518,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>288</v>
       </c>
@@ -4503,7 +4535,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>292</v>
       </c>
@@ -4520,7 +4552,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>295</v>
       </c>
@@ -4537,7 +4569,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>299</v>
       </c>
@@ -4554,7 +4586,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>304</v>
       </c>
@@ -4571,7 +4603,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>306</v>
       </c>
@@ -4588,7 +4620,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>310</v>
       </c>
@@ -4605,7 +4637,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>313</v>
       </c>
@@ -4622,7 +4654,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>316</v>
       </c>
@@ -4639,7 +4671,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>319</v>
       </c>
@@ -4656,7 +4688,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>322</v>
       </c>
@@ -4673,7 +4705,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>326</v>
       </c>
@@ -4690,7 +4722,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>329</v>
       </c>
@@ -4707,7 +4739,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>334</v>
       </c>
@@ -4724,7 +4756,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>338</v>
       </c>
@@ -4741,7 +4773,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>342</v>
       </c>
@@ -4758,7 +4790,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>346</v>
       </c>
@@ -4775,7 +4807,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>349</v>
       </c>
@@ -4792,7 +4824,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>352</v>
       </c>
@@ -4809,7 +4841,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>355</v>
       </c>
@@ -4826,7 +4858,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>358</v>
       </c>
@@ -4843,7 +4875,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>362</v>
       </c>
@@ -4860,7 +4892,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>365</v>
       </c>
@@ -4877,7 +4909,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>368</v>
       </c>
@@ -4894,7 +4926,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>372</v>
       </c>
@@ -4911,7 +4943,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>375</v>
       </c>
@@ -4928,7 +4960,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>378</v>
       </c>
@@ -4945,7 +4977,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>381</v>
       </c>
@@ -4962,7 +4994,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>384</v>
       </c>
@@ -4979,7 +5011,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>387</v>
       </c>
@@ -4996,7 +5028,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>390</v>
       </c>
@@ -5013,7 +5045,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>393</v>
       </c>
@@ -5030,7 +5062,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>396</v>
       </c>
@@ -5047,7 +5079,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>399</v>
       </c>
@@ -5064,7 +5096,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>403</v>
       </c>
@@ -5081,7 +5113,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>407</v>
       </c>
@@ -5098,7 +5130,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>411</v>
       </c>
@@ -5115,7 +5147,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>414</v>
       </c>
@@ -5132,7 +5164,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>417</v>
       </c>
@@ -5149,7 +5181,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>420</v>
       </c>
@@ -5166,7 +5198,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>423</v>
       </c>
@@ -5183,7 +5215,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>426</v>
       </c>
@@ -5200,7 +5232,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>429</v>
       </c>
@@ -5217,7 +5249,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>432</v>
       </c>
@@ -5234,7 +5266,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>435</v>
       </c>
@@ -5251,7 +5283,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>438</v>
       </c>
@@ -5268,7 +5300,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>441</v>
       </c>
@@ -5285,7 +5317,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>445</v>
       </c>
@@ -5302,7 +5334,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>448</v>
       </c>
@@ -5319,7 +5351,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>451</v>
       </c>
@@ -5336,7 +5368,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>454</v>
       </c>
@@ -5353,7 +5385,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>458</v>
       </c>
@@ -5370,7 +5402,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>463</v>
       </c>
@@ -5387,7 +5419,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>465</v>
       </c>
@@ -5404,7 +5436,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>470</v>
       </c>
@@ -5421,7 +5453,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>473</v>
       </c>
@@ -5438,7 +5470,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>476</v>
       </c>
@@ -5455,7 +5487,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>479</v>
       </c>
@@ -5486,7 +5518,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:L144"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
@@ -5502,7 +5534,7 @@
     <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" ht="24.75" customHeight="1">
+    <row r="1" spans="1:12" s="9" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5540,7 +5572,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -5578,7 +5610,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5616,7 +5648,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5654,7 +5686,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5692,7 +5724,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5730,7 +5762,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5768,7 +5800,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -5806,7 +5838,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -5844,7 +5876,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -5882,7 +5914,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -5920,7 +5952,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -5958,7 +5990,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -5996,7 +6028,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -6034,7 +6066,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -6072,7 +6104,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>50</v>
       </c>
@@ -6110,7 +6142,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>53</v>
       </c>
@@ -6148,7 +6180,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -6186,7 +6218,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -6224,7 +6256,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>60</v>
       </c>
@@ -6262,7 +6294,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -6300,7 +6332,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -6338,7 +6370,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -6376,7 +6408,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -6414,7 +6446,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -6452,7 +6484,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>82</v>
       </c>
@@ -6490,7 +6522,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>87</v>
       </c>
@@ -6528,7 +6560,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>299</v>
       </c>
@@ -6566,7 +6598,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>304</v>
       </c>
@@ -6604,7 +6636,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -6642,7 +6674,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -6680,7 +6712,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="32" spans="1:12">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -6718,7 +6750,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -6756,7 +6788,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -6794,7 +6826,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>106</v>
       </c>
@@ -6832,7 +6864,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -6870,7 +6902,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>112</v>
       </c>
@@ -6908,7 +6940,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -6946,7 +6978,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>118</v>
       </c>
@@ -6984,7 +7016,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>121</v>
       </c>
@@ -7022,7 +7054,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>124</v>
       </c>
@@ -7060,7 +7092,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>127</v>
       </c>
@@ -7098,7 +7130,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:12">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>130</v>
       </c>
@@ -7136,7 +7168,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="44" spans="1:12">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>133</v>
       </c>
@@ -7174,7 +7206,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="45" spans="1:12">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>192</v>
       </c>
@@ -7212,7 +7244,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>197</v>
       </c>
@@ -7250,7 +7282,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="47" spans="1:12">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -7288,7 +7320,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>203</v>
       </c>
@@ -7326,7 +7358,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -7364,7 +7396,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -7402,7 +7434,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="51" spans="1:12">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -7440,7 +7472,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>215</v>
       </c>
@@ -7478,7 +7510,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1">
+    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>334</v>
       </c>
@@ -7516,7 +7548,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="54" spans="1:12">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -7554,7 +7586,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="55" spans="1:12">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>136</v>
       </c>
@@ -7592,7 +7624,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="56" spans="1:12">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -7630,7 +7662,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>220</v>
       </c>
@@ -7668,7 +7700,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="58" spans="1:12">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>140</v>
       </c>
@@ -7706,7 +7738,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>144</v>
       </c>
@@ -7744,7 +7776,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="60" spans="1:12">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>147</v>
       </c>
@@ -7782,7 +7814,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="61" spans="1:12">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -7820,7 +7852,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="62" spans="1:12">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>259</v>
       </c>
@@ -7858,7 +7890,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="63" spans="1:12">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -7896,7 +7928,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="64" spans="1:12">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -7934,7 +7966,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="65" spans="1:12">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>268</v>
       </c>
@@ -7972,7 +8004,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="66" spans="1:12">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -8010,7 +8042,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="67" spans="1:12">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>154</v>
       </c>
@@ -8048,7 +8080,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="68" spans="1:12">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -8086,7 +8118,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="69" spans="1:12">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -8124,7 +8156,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="70" spans="1:12">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -8162,7 +8194,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="71" spans="1:12">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -8200,7 +8232,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="72" spans="1:12">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -8238,7 +8270,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="73" spans="1:12">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>172</v>
       </c>
@@ -8276,7 +8308,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="74" spans="1:12">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -8314,7 +8346,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="75" spans="1:12">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -8352,7 +8384,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="76" spans="1:12">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>306</v>
       </c>
@@ -8390,7 +8422,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="77" spans="1:12">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -8428,7 +8460,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="78" spans="1:12">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>313</v>
       </c>
@@ -8466,7 +8498,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="79" spans="1:12">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>316</v>
       </c>
@@ -8504,7 +8536,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="80" spans="1:12">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>319</v>
       </c>
@@ -8542,7 +8574,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="81" spans="1:12">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>342</v>
       </c>
@@ -8580,7 +8612,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="82" spans="1:12">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>346</v>
       </c>
@@ -8618,7 +8650,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="83" spans="1:12">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>349</v>
       </c>
@@ -8656,7 +8688,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="84" spans="1:12">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>507</v>
       </c>
@@ -8694,7 +8726,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:12">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>355</v>
       </c>
@@ -8732,7 +8764,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="86" spans="1:12">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>358</v>
       </c>
@@ -8770,7 +8802,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="87" spans="1:12">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>362</v>
       </c>
@@ -8808,7 +8840,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="88" spans="1:12">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>365</v>
       </c>
@@ -8846,7 +8878,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="89" spans="1:12">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -8884,7 +8916,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="90" spans="1:12">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -8922,7 +8954,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="91" spans="1:12">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -8960,7 +8992,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="92" spans="1:12">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>181</v>
       </c>
@@ -8998,7 +9030,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="93" spans="1:12">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -9036,7 +9068,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="94" spans="1:12">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -9074,7 +9106,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="95" spans="1:12">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>282</v>
       </c>
@@ -9112,7 +9144,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="96" spans="1:12">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -9150,7 +9182,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="97" spans="1:12">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>288</v>
       </c>
@@ -9188,7 +9220,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="98" spans="1:12">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>368</v>
       </c>
@@ -9226,7 +9258,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="99" spans="1:12">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>372</v>
       </c>
@@ -9264,7 +9296,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="100" spans="1:12">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>375</v>
       </c>
@@ -9302,7 +9334,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="101" spans="1:12">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -9340,7 +9372,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="102" spans="1:12">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>381</v>
       </c>
@@ -9378,7 +9410,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="103" spans="1:12">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -9416,7 +9448,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="104" spans="1:12">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -9454,7 +9486,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="105" spans="1:12">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>390</v>
       </c>
@@ -9492,7 +9524,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="106" spans="1:12">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -9530,7 +9562,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="107" spans="1:12">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -9568,7 +9600,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="108" spans="1:12">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>479</v>
       </c>
@@ -9606,7 +9638,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="109" spans="1:12">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -9644,7 +9676,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="110" spans="1:12">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -9682,7 +9714,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="111" spans="1:12">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -9720,7 +9752,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="112" spans="1:12">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -9758,7 +9790,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="113" spans="1:12">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>473</v>
       </c>
@@ -9796,7 +9828,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="114" spans="1:12">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -9834,7 +9866,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="115" spans="1:12">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -9872,7 +9904,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="116" spans="1:12">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>189</v>
       </c>
@@ -9910,7 +9942,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="117" spans="1:12">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -9948,7 +9980,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="118" spans="1:12">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>224</v>
       </c>
@@ -9986,7 +10018,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="119" spans="1:12">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>228</v>
       </c>
@@ -10024,7 +10056,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="120" spans="1:12">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -10062,7 +10094,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="121" spans="1:12">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>234</v>
       </c>
@@ -10100,7 +10132,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="122" spans="1:12">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -10138,7 +10170,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="123" spans="1:12">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>240</v>
       </c>
@@ -10176,7 +10208,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="124" spans="1:12">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>243</v>
       </c>
@@ -10214,7 +10246,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="125" spans="1:12">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -10252,7 +10284,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="126" spans="1:12">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>295</v>
       </c>
@@ -10290,7 +10322,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="127" spans="1:12">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>322</v>
       </c>
@@ -10328,7 +10360,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="128" spans="1:12">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>326</v>
       </c>
@@ -10366,7 +10398,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="129" spans="1:12">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>407</v>
       </c>
@@ -10404,7 +10436,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="130" spans="1:12">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
         <v>411</v>
       </c>
@@ -10442,7 +10474,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="131" spans="1:12">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>414</v>
       </c>
@@ -10480,7 +10512,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="132" spans="1:12">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>417</v>
       </c>
@@ -10518,7 +10550,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="133" spans="1:12">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>420</v>
       </c>
@@ -10556,7 +10588,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="134" spans="1:12">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -10594,7 +10626,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="135" spans="1:12">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>426</v>
       </c>
@@ -10632,7 +10664,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="136" spans="1:12">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>429</v>
       </c>
@@ -10670,7 +10702,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="137" spans="1:12">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -10708,7 +10740,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="138" spans="1:12">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>435</v>
       </c>
@@ -10746,7 +10778,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="139" spans="1:12">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>438</v>
       </c>
@@ -10784,7 +10816,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="140" spans="1:12">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -10822,7 +10854,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="141" spans="1:12">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -10860,7 +10892,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="142" spans="1:12">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -10898,7 +10930,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="143" spans="1:12">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -10936,7 +10968,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="144" spans="1:12">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -10987,7 +11019,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:G146"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.28515625" customWidth="1"/>
     <col min="2" max="3" width="16.85546875" style="8" customWidth="1"/>
@@ -10997,7 +11029,7 @@
     <col min="7" max="7" width="24.85546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" customHeight="1">
+    <row r="1" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11020,7 +11052,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -11043,7 +11075,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -11066,7 +11098,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -11089,7 +11121,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -11112,7 +11144,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -11135,7 +11167,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -11158,7 +11190,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -11181,7 +11213,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -11204,7 +11236,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -11227,7 +11259,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -11250,7 +11282,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -11273,7 +11305,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -11296,7 +11328,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -11319,7 +11351,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -11342,7 +11374,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -11365,7 +11397,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -11388,7 +11420,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -11411,7 +11443,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -11434,7 +11466,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>60</v>
       </c>
@@ -11457,7 +11489,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -11480,7 +11512,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -11505,7 +11537,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -11530,7 +11562,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -11555,7 +11587,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -11580,7 +11612,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -11603,7 +11635,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -11628,7 +11660,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>299</v>
       </c>
@@ -11653,7 +11685,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>304</v>
       </c>
@@ -11678,7 +11710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -11703,7 +11735,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -11728,7 +11760,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>517</v>
       </c>
@@ -11753,7 +11785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -11776,7 +11808,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -11799,7 +11831,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
@@ -11824,7 +11856,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -11849,7 +11881,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -11874,7 +11906,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -11899,7 +11931,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -11924,7 +11956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
@@ -11949,7 +11981,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -11974,7 +12006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -11999,7 +12031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -12024,7 +12056,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
@@ -12049,7 +12081,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>192</v>
       </c>
@@ -12072,7 +12104,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
@@ -12095,7 +12127,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -12118,7 +12150,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>203</v>
       </c>
@@ -12141,7 +12173,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -12164,7 +12196,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -12187,7 +12219,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -12210,7 +12242,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>215</v>
       </c>
@@ -12233,7 +12265,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>334</v>
       </c>
@@ -12256,7 +12288,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -12279,7 +12311,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -12304,7 +12336,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -12329,7 +12361,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>220</v>
       </c>
@@ -12352,7 +12384,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>140</v>
       </c>
@@ -12377,7 +12409,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>144</v>
       </c>
@@ -12402,7 +12434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>147</v>
       </c>
@@ -12427,7 +12459,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -12450,7 +12482,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>259</v>
       </c>
@@ -12473,7 +12505,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -12496,7 +12528,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -12519,7 +12551,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>268</v>
       </c>
@@ -12542,7 +12574,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -12565,7 +12597,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -12590,7 +12622,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -12615,7 +12647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -12640,7 +12672,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -12665,7 +12697,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -12688,7 +12720,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -12711,7 +12743,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
@@ -12736,7 +12768,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -12759,7 +12791,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -12782,7 +12814,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>306</v>
       </c>
@@ -12807,7 +12839,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>310</v>
       </c>
@@ -12832,7 +12864,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>313</v>
       </c>
@@ -12857,7 +12889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>316</v>
       </c>
@@ -12882,7 +12914,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>319</v>
       </c>
@@ -12907,7 +12939,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>342</v>
       </c>
@@ -12930,7 +12962,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>346</v>
       </c>
@@ -12953,7 +12985,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>349</v>
       </c>
@@ -12976,7 +13008,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -12999,7 +13031,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
@@ -13022,7 +13054,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>358</v>
       </c>
@@ -13045,7 +13077,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -13068,7 +13100,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>365</v>
       </c>
@@ -13091,7 +13123,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -13114,7 +13146,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -13137,7 +13169,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -13160,7 +13192,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -13185,7 +13217,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -13208,7 +13240,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -13231,7 +13263,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>282</v>
       </c>
@@ -13254,7 +13286,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -13277,7 +13309,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>288</v>
       </c>
@@ -13300,7 +13332,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>368</v>
       </c>
@@ -13323,7 +13355,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>372</v>
       </c>
@@ -13346,7 +13378,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>375</v>
       </c>
@@ -13369,7 +13401,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -13392,7 +13424,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>381</v>
       </c>
@@ -13415,7 +13447,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -13438,7 +13470,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -13461,7 +13493,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>390</v>
       </c>
@@ -13484,7 +13516,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -13507,7 +13539,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -13530,7 +13562,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>479</v>
       </c>
@@ -13553,7 +13585,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -13576,7 +13608,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -13599,7 +13631,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -13624,7 +13656,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -13649,7 +13681,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>473</v>
       </c>
@@ -13674,7 +13706,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -13697,7 +13729,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -13720,7 +13752,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
@@ -13745,7 +13777,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -13768,7 +13800,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -13791,7 +13823,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>228</v>
       </c>
@@ -13814,7 +13846,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -13837,7 +13869,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>234</v>
       </c>
@@ -13860,7 +13892,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -13883,7 +13915,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>240</v>
       </c>
@@ -13906,7 +13938,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>243</v>
       </c>
@@ -13929,7 +13961,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -13952,7 +13984,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>295</v>
       </c>
@@ -13975,7 +14007,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>322</v>
       </c>
@@ -14000,7 +14032,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -14025,7 +14057,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>407</v>
       </c>
@@ -14048,7 +14080,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>411</v>
       </c>
@@ -14071,7 +14103,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>414</v>
       </c>
@@ -14094,7 +14126,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>417</v>
       </c>
@@ -14117,7 +14149,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>420</v>
       </c>
@@ -14140,7 +14172,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -14163,7 +14195,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>426</v>
       </c>
@@ -14186,7 +14218,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>429</v>
       </c>
@@ -14209,7 +14241,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -14232,7 +14264,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>435</v>
       </c>
@@ -14255,7 +14287,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>438</v>
       </c>
@@ -14278,7 +14310,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -14301,7 +14333,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -14324,7 +14356,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -14347,7 +14379,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -14370,7 +14402,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -14393,10 +14425,10 @@
         <v>516</v>
       </c>
     </row>
-    <row r="145" spans="1:1">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:1">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
     </row>
   </sheetData>
@@ -14412,7 +14444,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:R181"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -14431,7 +14463,7 @@
     <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -14487,7 +14519,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -14543,7 +14575,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -14599,7 +14631,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -14655,7 +14687,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -14711,7 +14743,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -14767,7 +14799,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -14823,7 +14855,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -14879,7 +14911,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -14935,7 +14967,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -14991,7 +15023,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -15047,7 +15079,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -15103,7 +15135,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -15159,7 +15191,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -15215,7 +15247,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -15271,7 +15303,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
         <v>50</v>
       </c>
@@ -15327,7 +15359,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>53</v>
       </c>
@@ -15383,7 +15415,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -15439,7 +15471,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -15495,7 +15527,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>60</v>
       </c>
@@ -15551,7 +15583,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -15607,7 +15639,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -15663,7 +15695,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -15719,7 +15751,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -15775,7 +15807,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -15831,7 +15863,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>82</v>
       </c>
@@ -15887,7 +15919,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>87</v>
       </c>
@@ -15943,7 +15975,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>299</v>
       </c>
@@ -15999,7 +16031,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>304</v>
       </c>
@@ -16055,7 +16087,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -16111,7 +16143,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -16167,7 +16199,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -16223,7 +16255,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -16279,7 +16311,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -16335,7 +16367,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>106</v>
       </c>
@@ -16391,7 +16423,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="36" spans="1:18">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -16447,7 +16479,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="37" spans="1:18">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>112</v>
       </c>
@@ -16503,7 +16535,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="38" spans="1:18">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -16559,7 +16591,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="39" spans="1:18">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>118</v>
       </c>
@@ -16615,7 +16647,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="40" spans="1:18">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
         <v>121</v>
       </c>
@@ -16671,7 +16703,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="41" spans="1:18">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="10" t="s">
         <v>124</v>
       </c>
@@ -16727,7 +16759,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="42" spans="1:18">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
         <v>127</v>
       </c>
@@ -16783,7 +16815,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="43" spans="1:18">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="10" t="s">
         <v>130</v>
       </c>
@@ -16839,7 +16871,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="44" spans="1:18">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
         <v>133</v>
       </c>
@@ -16895,7 +16927,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" spans="1:18">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>192</v>
       </c>
@@ -16951,7 +16983,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="46" spans="1:18">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
         <v>197</v>
       </c>
@@ -17007,7 +17039,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="47" spans="1:18">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -17063,7 +17095,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="48" spans="1:18">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
         <v>203</v>
       </c>
@@ -17119,7 +17151,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:18">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -17175,7 +17207,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="50" spans="1:18">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -17231,7 +17263,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -17287,7 +17319,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="52" spans="1:18">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
         <v>215</v>
       </c>
@@ -17343,7 +17375,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="53" spans="1:18">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>334</v>
       </c>
@@ -17399,7 +17431,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="54" spans="1:18">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -17455,7 +17487,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="55" spans="1:18">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>136</v>
       </c>
@@ -17511,7 +17543,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="56" spans="1:18">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -17567,7 +17599,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="57" spans="1:18">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="10" t="s">
         <v>220</v>
       </c>
@@ -17623,7 +17655,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="58" spans="1:18">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
         <v>140</v>
       </c>
@@ -17679,7 +17711,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="59" spans="1:18">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
         <v>144</v>
       </c>
@@ -17735,7 +17767,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="60" spans="1:18">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
         <v>147</v>
       </c>
@@ -17791,7 +17823,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="61" spans="1:18">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -17847,7 +17879,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="62" spans="1:18">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
         <v>259</v>
       </c>
@@ -17903,7 +17935,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="63" spans="1:18">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -17959,7 +17991,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="64" spans="1:18">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -18015,7 +18047,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="65" spans="1:18">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
         <v>268</v>
       </c>
@@ -18071,7 +18103,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" spans="1:18">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -18127,7 +18159,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="67" spans="1:18">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>154</v>
       </c>
@@ -18183,7 +18215,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="68" spans="1:18">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -18239,7 +18271,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="69" spans="1:18">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -18295,7 +18327,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="70" spans="1:18">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -18351,7 +18383,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="71" spans="1:18">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -18407,7 +18439,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="72" spans="1:18">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -18463,7 +18495,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="73" spans="1:18">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>172</v>
       </c>
@@ -18519,7 +18551,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="74" spans="1:18">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -18575,7 +18607,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="75" spans="1:18">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -18631,7 +18663,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="76" spans="1:18">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>306</v>
       </c>
@@ -18687,7 +18719,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="77" spans="1:18">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -18743,7 +18775,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="78" spans="1:18">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>313</v>
       </c>
@@ -18799,7 +18831,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="79" spans="1:18">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
         <v>316</v>
       </c>
@@ -18855,7 +18887,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="80" spans="1:18">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
         <v>319</v>
       </c>
@@ -18911,7 +18943,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="81" spans="1:18">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
         <v>342</v>
       </c>
@@ -18967,7 +18999,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="82" spans="1:18">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
         <v>346</v>
       </c>
@@ -19023,7 +19055,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="83" spans="1:18">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
         <v>349</v>
       </c>
@@ -19079,7 +19111,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="84" spans="1:18">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
         <v>507</v>
       </c>
@@ -19135,7 +19167,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="85" spans="1:18">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
         <v>355</v>
       </c>
@@ -19191,7 +19223,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="86" spans="1:18">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
         <v>358</v>
       </c>
@@ -19247,7 +19279,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="87" spans="1:18">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
         <v>362</v>
       </c>
@@ -19303,7 +19335,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="88" spans="1:18">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
         <v>365</v>
       </c>
@@ -19359,7 +19391,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="89" spans="1:18">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -19415,7 +19447,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="1:18">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -19471,7 +19503,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="91" spans="1:18">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -19527,7 +19559,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="92" spans="1:18">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
         <v>181</v>
       </c>
@@ -19583,7 +19615,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="93" spans="1:18">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -19639,7 +19671,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="94" spans="1:18">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -19695,7 +19727,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="95" spans="1:18">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
         <v>282</v>
       </c>
@@ -19751,7 +19783,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="96" spans="1:18">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -19807,7 +19839,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="1:18">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
         <v>288</v>
       </c>
@@ -19863,7 +19895,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="98" spans="1:18">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
         <v>368</v>
       </c>
@@ -19919,7 +19951,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="99" spans="1:18">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
         <v>372</v>
       </c>
@@ -19975,7 +20007,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="100" spans="1:18">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
         <v>375</v>
       </c>
@@ -20031,7 +20063,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="101" spans="1:18">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -20087,7 +20119,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="102" spans="1:18">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
         <v>381</v>
       </c>
@@ -20143,7 +20175,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="103" spans="1:18">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -20199,7 +20231,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="104" spans="1:18">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -20255,7 +20287,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="105" spans="1:18">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>390</v>
       </c>
@@ -20311,7 +20343,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="106" spans="1:18">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -20367,7 +20399,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="107" spans="1:18">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -20423,7 +20455,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="108" spans="1:18">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
         <v>479</v>
       </c>
@@ -20479,7 +20511,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="109" spans="1:18">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -20535,7 +20567,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="110" spans="1:18">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -20591,7 +20623,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="111" spans="1:18">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -20647,7 +20679,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="112" spans="1:18">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -20703,7 +20735,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="113" spans="1:18">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
         <v>473</v>
       </c>
@@ -20759,7 +20791,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="114" spans="1:18">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -20815,7 +20847,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="115" spans="1:18">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -20871,7 +20903,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="116" spans="1:18">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
         <v>189</v>
       </c>
@@ -20927,7 +20959,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="117" spans="1:18">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -20983,7 +21015,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="118" spans="1:18">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
         <v>224</v>
       </c>
@@ -21039,7 +21071,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="119" spans="1:18">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
         <v>228</v>
       </c>
@@ -21095,7 +21127,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="120" spans="1:18">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -21151,7 +21183,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="121" spans="1:18">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
         <v>234</v>
       </c>
@@ -21207,7 +21239,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="122" spans="1:18">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -21263,7 +21295,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="123" spans="1:18">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
         <v>240</v>
       </c>
@@ -21319,7 +21351,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="124" spans="1:18">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
         <v>243</v>
       </c>
@@ -21375,7 +21407,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="125" spans="1:18">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -21431,7 +21463,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="126" spans="1:18">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
         <v>295</v>
       </c>
@@ -21487,7 +21519,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="127" spans="1:18">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
         <v>322</v>
       </c>
@@ -21543,7 +21575,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="128" spans="1:18">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
         <v>326</v>
       </c>
@@ -21599,7 +21631,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="129" spans="1:18">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
         <v>407</v>
       </c>
@@ -21655,7 +21687,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="130" spans="1:18">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
         <v>411</v>
       </c>
@@ -21711,7 +21743,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="131" spans="1:18">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
         <v>414</v>
       </c>
@@ -21767,7 +21799,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="132" spans="1:18">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
         <v>417</v>
       </c>
@@ -21823,7 +21855,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="133" spans="1:18">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
         <v>420</v>
       </c>
@@ -21879,7 +21911,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="134" spans="1:18">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -21935,7 +21967,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="135" spans="1:18">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
         <v>426</v>
       </c>
@@ -21991,7 +22023,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="136" spans="1:18">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
         <v>429</v>
       </c>
@@ -22047,7 +22079,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="137" spans="1:18">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -22103,7 +22135,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="138" spans="1:18">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
         <v>435</v>
       </c>
@@ -22159,7 +22191,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="139" spans="1:18">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
         <v>438</v>
       </c>
@@ -22215,7 +22247,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="140" spans="1:18">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -22271,7 +22303,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="141" spans="1:18">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -22327,7 +22359,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="142" spans="1:18">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -22383,7 +22415,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="143" spans="1:18">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -22439,7 +22471,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="144" spans="1:18">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -22495,115 +22527,115 @@
         <v>557</v>
       </c>
     </row>
-    <row r="145" spans="2:2">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B145" s="1"/>
     </row>
-    <row r="146" spans="2:2">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B146" s="1"/>
     </row>
-    <row r="147" spans="2:2">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B147" s="1"/>
     </row>
-    <row r="148" spans="2:2">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B148" s="1"/>
     </row>
-    <row r="149" spans="2:2">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B149" s="1"/>
     </row>
-    <row r="150" spans="2:2">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B150" s="1"/>
     </row>
-    <row r="151" spans="2:2">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B151" s="1"/>
     </row>
-    <row r="152" spans="2:2">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B152" s="1"/>
     </row>
-    <row r="153" spans="2:2">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B153" s="1"/>
     </row>
-    <row r="154" spans="2:2">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B154" s="1"/>
     </row>
-    <row r="155" spans="2:2">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B155" s="1"/>
     </row>
-    <row r="156" spans="2:2">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B156" s="1"/>
     </row>
-    <row r="157" spans="2:2">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B157" s="1"/>
     </row>
-    <row r="158" spans="2:2">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B158" s="1"/>
     </row>
-    <row r="159" spans="2:2">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B159" s="1"/>
     </row>
-    <row r="160" spans="2:2">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B160" s="1"/>
     </row>
-    <row r="161" spans="2:2">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B161" s="1"/>
     </row>
-    <row r="162" spans="2:2">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B162" s="1"/>
     </row>
-    <row r="163" spans="2:2">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B163" s="1"/>
     </row>
-    <row r="164" spans="2:2">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B164" s="1"/>
     </row>
-    <row r="165" spans="2:2">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B165" s="1"/>
     </row>
-    <row r="166" spans="2:2">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B166" s="1"/>
     </row>
-    <row r="167" spans="2:2">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B167" s="1"/>
     </row>
-    <row r="168" spans="2:2">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B168" s="1"/>
     </row>
-    <row r="169" spans="2:2">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B169" s="1"/>
     </row>
-    <row r="170" spans="2:2">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B170" s="1"/>
     </row>
-    <row r="171" spans="2:2">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B171" s="1"/>
     </row>
-    <row r="172" spans="2:2">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B172" s="1"/>
     </row>
-    <row r="173" spans="2:2">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B173" s="1"/>
     </row>
-    <row r="174" spans="2:2">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B174" s="1"/>
     </row>
-    <row r="175" spans="2:2">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B175" s="1"/>
     </row>
-    <row r="176" spans="2:2">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B176" s="1"/>
     </row>
-    <row r="177" spans="2:2">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B177" s="1"/>
     </row>
-    <row r="178" spans="2:2">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B178" s="1"/>
     </row>
-    <row r="179" spans="2:2">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B179" s="1"/>
     </row>
-    <row r="180" spans="2:2">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B180" s="1"/>
     </row>
-    <row r="181" spans="2:2">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B181" s="1"/>
     </row>
   </sheetData>
@@ -22616,7 +22648,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:P144"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.85546875" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" style="7" customWidth="1"/>
@@ -22627,7 +22659,7 @@
     <col min="11" max="11" width="22.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -22650,7 +22682,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -22673,7 +22705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -22696,7 +22728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -22719,7 +22751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -22742,7 +22774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -22765,7 +22797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -22792,7 +22824,7 @@
       <c r="M7" s="14"/>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -22819,7 +22851,7 @@
       <c r="M8" s="16"/>
       <c r="N8" s="15"/>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -22846,7 +22878,7 @@
       <c r="M9" s="18"/>
       <c r="N9" s="15"/>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -22873,7 +22905,7 @@
       <c r="M10" s="16"/>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -22900,7 +22932,7 @@
       <c r="M11" s="16"/>
       <c r="N11" s="15"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -22923,7 +22955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -22946,7 +22978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -22969,7 +23001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -22992,7 +23024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -23015,7 +23047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -23038,7 +23070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -23061,7 +23093,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -23084,7 +23116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>60</v>
       </c>
@@ -23107,7 +23139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -23130,7 +23162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -23153,7 +23185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -23176,7 +23208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -23199,7 +23231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -23222,7 +23254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -23245,7 +23277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -23268,7 +23300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>299</v>
       </c>
@@ -23291,7 +23323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>304</v>
       </c>
@@ -23314,7 +23346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -23337,7 +23369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -23360,7 +23392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
@@ -23383,7 +23415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -23406,7 +23438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -23429,7 +23461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
@@ -23452,7 +23484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -23475,7 +23507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -23498,7 +23530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -23521,7 +23553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -23544,7 +23576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
@@ -23567,7 +23599,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -23590,7 +23622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -23613,7 +23645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -23636,7 +23668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
@@ -23659,7 +23691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>192</v>
       </c>
@@ -23682,7 +23714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
@@ -23705,7 +23737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -23728,7 +23760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>203</v>
       </c>
@@ -23751,7 +23783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -23774,7 +23806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -23797,7 +23829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -23820,7 +23852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>215</v>
       </c>
@@ -23843,7 +23875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>334</v>
       </c>
@@ -23866,7 +23898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -23889,7 +23921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -23912,7 +23944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -23935,7 +23967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>220</v>
       </c>
@@ -23958,7 +23990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>140</v>
       </c>
@@ -23981,7 +24013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>144</v>
       </c>
@@ -24004,7 +24036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>147</v>
       </c>
@@ -24027,7 +24059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -24054,7 +24086,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="15"/>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>259</v>
       </c>
@@ -24081,7 +24113,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="15"/>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -24108,7 +24140,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="15"/>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -24135,7 +24167,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="15"/>
     </row>
-    <row r="65" spans="1:14">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>268</v>
       </c>
@@ -24162,7 +24194,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="15"/>
     </row>
-    <row r="66" spans="1:14">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -24189,7 +24221,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="15"/>
     </row>
-    <row r="67" spans="1:14">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -24216,7 +24248,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="15"/>
     </row>
-    <row r="68" spans="1:14">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>157</v>
       </c>
@@ -24243,7 +24275,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="15"/>
     </row>
-    <row r="69" spans="1:14">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -24270,7 +24302,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="15"/>
     </row>
-    <row r="70" spans="1:14">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -24297,7 +24329,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="15"/>
     </row>
-    <row r="71" spans="1:14">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>166</v>
       </c>
@@ -24324,7 +24356,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="15"/>
     </row>
-    <row r="72" spans="1:14">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -24351,7 +24383,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="15"/>
     </row>
-    <row r="73" spans="1:14">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
@@ -24378,7 +24410,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="15"/>
     </row>
-    <row r="74" spans="1:14">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -24405,7 +24437,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="15"/>
     </row>
-    <row r="75" spans="1:14">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -24432,7 +24464,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="15"/>
     </row>
-    <row r="76" spans="1:14">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>306</v>
       </c>
@@ -24459,7 +24491,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="15"/>
     </row>
-    <row r="77" spans="1:14">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>310</v>
       </c>
@@ -24486,7 +24518,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="15"/>
     </row>
-    <row r="78" spans="1:14">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>313</v>
       </c>
@@ -24510,7 +24542,7 @@
       </c>
       <c r="N78" s="15"/>
     </row>
-    <row r="79" spans="1:14">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>316</v>
       </c>
@@ -24537,7 +24569,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="15"/>
     </row>
-    <row r="80" spans="1:14">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>319</v>
       </c>
@@ -24564,7 +24596,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="15"/>
     </row>
-    <row r="81" spans="1:14">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>342</v>
       </c>
@@ -24591,7 +24623,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="15"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>346</v>
       </c>
@@ -24618,7 +24650,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="15"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>349</v>
       </c>
@@ -24645,7 +24677,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="15"/>
     </row>
-    <row r="84" spans="1:14">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -24672,7 +24704,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="15"/>
     </row>
-    <row r="85" spans="1:14">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
@@ -24699,7 +24731,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="15"/>
     </row>
-    <row r="86" spans="1:14">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>358</v>
       </c>
@@ -24722,7 +24754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -24745,7 +24777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>365</v>
       </c>
@@ -24768,7 +24800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -24791,7 +24823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -24814,7 +24846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -24837,7 +24869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -24860,7 +24892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -24883,7 +24915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -24906,7 +24938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>282</v>
       </c>
@@ -24929,7 +24961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -24952,7 +24984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>288</v>
       </c>
@@ -24975,7 +25007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>368</v>
       </c>
@@ -24998,7 +25030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>372</v>
       </c>
@@ -25021,7 +25053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>375</v>
       </c>
@@ -25044,7 +25076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -25067,7 +25099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>381</v>
       </c>
@@ -25090,7 +25122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -25113,7 +25145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -25136,7 +25168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>390</v>
       </c>
@@ -25159,7 +25191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -25182,7 +25214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -25205,7 +25237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>479</v>
       </c>
@@ -25228,7 +25260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -25251,7 +25283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -25274,7 +25306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -25297,7 +25329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -25320,7 +25352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>473</v>
       </c>
@@ -25343,7 +25375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -25366,7 +25398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -25389,7 +25421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
@@ -25412,7 +25444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -25435,7 +25467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -25458,7 +25490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>228</v>
       </c>
@@ -25481,7 +25513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -25504,7 +25536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>234</v>
       </c>
@@ -25527,7 +25559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -25550,7 +25582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>240</v>
       </c>
@@ -25573,7 +25605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>243</v>
       </c>
@@ -25596,7 +25628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -25619,7 +25651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>295</v>
       </c>
@@ -25642,7 +25674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>322</v>
       </c>
@@ -25665,7 +25697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -25688,7 +25720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>407</v>
       </c>
@@ -25711,7 +25743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>411</v>
       </c>
@@ -25734,7 +25766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>414</v>
       </c>
@@ -25757,7 +25789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>417</v>
       </c>
@@ -25780,7 +25812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:16">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>420</v>
       </c>
@@ -25803,7 +25835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -25826,7 +25858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>426</v>
       </c>
@@ -25849,7 +25881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>429</v>
       </c>
@@ -25872,7 +25904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -25898,7 +25930,7 @@
       <c r="O137" s="15"/>
       <c r="P137" s="16"/>
     </row>
-    <row r="138" spans="1:16">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>435</v>
       </c>
@@ -25921,7 +25953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:16">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>438</v>
       </c>
@@ -25944,7 +25976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -25967,7 +25999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -25990,7 +26022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -26013,7 +26045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -26036,7 +26068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -26068,7 +26100,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J144"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
     <col min="2" max="2" width="23.7109375" style="10" bestFit="1" customWidth="1"/>
@@ -26077,7 +26109,7 @@
     <col min="7" max="10" width="18.7109375" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.9" customHeight="1">
+    <row r="1" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -26109,7 +26141,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" customHeight="1">
+    <row r="2" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -26139,7 +26171,7 @@
         <v>25288</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -26171,7 +26203,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -26203,7 +26235,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.45" customHeight="1">
+    <row r="5" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -26235,7 +26267,7 @@
         <v>147076</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -26267,7 +26299,7 @@
         <v>106576</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -26299,7 +26331,7 @@
         <v>57176</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -26331,7 +26363,7 @@
         <v>37912</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -26363,7 +26395,7 @@
         <v>138608</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -26395,7 +26427,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -26427,7 +26459,7 @@
         <v>5712</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -26459,7 +26491,7 @@
         <v>6528</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -26491,7 +26523,7 @@
         <v>10784</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -26523,7 +26555,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -26555,7 +26587,7 @@
         <v>195096</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -26587,7 +26619,7 @@
         <v>38224</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -26619,7 +26651,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.45" customHeight="1">
+    <row r="18" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -26651,7 +26683,7 @@
         <v>28388</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -26683,7 +26715,7 @@
         <v>4784</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.45" customHeight="1">
+    <row r="20" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>60</v>
       </c>
@@ -26715,7 +26747,7 @@
         <v>62592</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -26747,7 +26779,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -26779,7 +26811,7 @@
         <v>27532</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -26811,7 +26843,7 @@
         <v>129388</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -26843,7 +26875,7 @@
         <v>126700</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -26875,7 +26907,7 @@
         <v>19516</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -26907,7 +26939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.45" customHeight="1">
+    <row r="27" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -26939,7 +26971,7 @@
         <v>41284</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>299</v>
       </c>
@@ -26971,7 +27003,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.45" customHeight="1">
+    <row r="29" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>304</v>
       </c>
@@ -27003,7 +27035,7 @@
         <v>119388</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -27035,7 +27067,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -27067,7 +27099,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
@@ -27099,7 +27131,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -27131,7 +27163,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -27163,7 +27195,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
@@ -27195,7 +27227,7 @@
         <v>30076</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -27227,7 +27259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -27259,7 +27291,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -27291,7 +27323,7 @@
         <v>3256</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -27323,7 +27355,7 @@
         <v>8324</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14.45" customHeight="1">
+    <row r="40" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
@@ -27355,7 +27387,7 @@
         <v>30920</v>
       </c>
     </row>
-    <row r="41" spans="1:10">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -27387,7 +27419,7 @@
         <v>3376</v>
       </c>
     </row>
-    <row r="42" spans="1:10">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -27419,7 +27451,7 @@
         <v>182600</v>
       </c>
     </row>
-    <row r="43" spans="1:10">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -27451,7 +27483,7 @@
         <v>80984</v>
       </c>
     </row>
-    <row r="44" spans="1:10">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
@@ -27483,7 +27515,7 @@
         <v>25232</v>
       </c>
     </row>
-    <row r="45" spans="1:10">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>192</v>
       </c>
@@ -27515,7 +27547,7 @@
         <v>9804</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.45" customHeight="1">
+    <row r="46" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
@@ -27547,7 +27579,7 @@
         <v>64768</v>
       </c>
     </row>
-    <row r="47" spans="1:10">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -27579,7 +27611,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="48" spans="1:10">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>203</v>
       </c>
@@ -27611,7 +27643,7 @@
         <v>4796</v>
       </c>
     </row>
-    <row r="49" spans="1:10">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -27643,7 +27675,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="50" spans="1:10">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -27675,7 +27707,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="51" spans="1:10">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -27707,7 +27739,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="52" spans="1:10">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>215</v>
       </c>
@@ -27739,7 +27771,7 @@
         <v>94976</v>
       </c>
     </row>
-    <row r="53" spans="1:10">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>334</v>
       </c>
@@ -27771,7 +27803,7 @@
         <v>88892</v>
       </c>
     </row>
-    <row r="54" spans="1:10">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -27803,7 +27835,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="55" spans="1:10">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -27835,7 +27867,7 @@
         <v>149804</v>
       </c>
     </row>
-    <row r="56" spans="1:10">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -27867,7 +27899,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="57" spans="1:10">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>220</v>
       </c>
@@ -27899,7 +27931,7 @@
         <v>7776</v>
       </c>
     </row>
-    <row r="58" spans="1:10">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>140</v>
       </c>
@@ -27931,7 +27963,7 @@
         <v>55688</v>
       </c>
     </row>
-    <row r="59" spans="1:10">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>144</v>
       </c>
@@ -27963,7 +27995,7 @@
         <v>91276</v>
       </c>
     </row>
-    <row r="60" spans="1:10">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>147</v>
       </c>
@@ -27995,7 +28027,7 @@
         <v>73244</v>
       </c>
     </row>
-    <row r="61" spans="1:10">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -28027,7 +28059,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="62" spans="1:10">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>259</v>
       </c>
@@ -28059,7 +28091,7 @@
         <v>42320</v>
       </c>
     </row>
-    <row r="63" spans="1:10">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -28091,7 +28123,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="1:10">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -28123,7 +28155,7 @@
         <v>8564</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>268</v>
       </c>
@@ -28155,7 +28187,7 @@
         <v>32848</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -28187,7 +28219,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -28219,7 +28251,7 @@
         <v>227176</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>157</v>
       </c>
@@ -28251,7 +28283,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -28283,7 +28315,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -28315,7 +28347,7 @@
         <v>25824</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>166</v>
       </c>
@@ -28347,7 +28379,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -28379,7 +28411,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
@@ -28411,7 +28443,7 @@
         <v>47244</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -28443,7 +28475,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -28475,7 +28507,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>306</v>
       </c>
@@ -28507,7 +28539,7 @@
         <v>34392</v>
       </c>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>310</v>
       </c>
@@ -28539,7 +28571,7 @@
         <v>32772</v>
       </c>
     </row>
-    <row r="78" spans="1:10">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>313</v>
       </c>
@@ -28571,7 +28603,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="79" spans="1:10">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>316</v>
       </c>
@@ -28603,7 +28635,7 @@
         <v>88524</v>
       </c>
     </row>
-    <row r="80" spans="1:10">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>319</v>
       </c>
@@ -28635,7 +28667,7 @@
         <v>41020</v>
       </c>
     </row>
-    <row r="81" spans="1:10">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>342</v>
       </c>
@@ -28667,7 +28699,7 @@
         <v>7848</v>
       </c>
     </row>
-    <row r="82" spans="1:10">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>346</v>
       </c>
@@ -28699,7 +28731,7 @@
         <v>8888</v>
       </c>
     </row>
-    <row r="83" spans="1:10">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>349</v>
       </c>
@@ -28731,7 +28763,7 @@
         <v>24704</v>
       </c>
     </row>
-    <row r="84" spans="1:10">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -28763,7 +28795,7 @@
         <v>21076</v>
       </c>
     </row>
-    <row r="85" spans="1:10">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
@@ -28795,7 +28827,7 @@
         <v>27036</v>
       </c>
     </row>
-    <row r="86" spans="1:10">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>358</v>
       </c>
@@ -28827,7 +28859,7 @@
         <v>164072</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="14.45" customHeight="1">
+    <row r="87" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -28859,7 +28891,7 @@
         <v>42516</v>
       </c>
     </row>
-    <row r="88" spans="1:10">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>365</v>
       </c>
@@ -28891,7 +28923,7 @@
         <v>145640</v>
       </c>
     </row>
-    <row r="89" spans="1:10">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -28923,7 +28955,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="90" spans="1:10">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -28955,7 +28987,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="1:10">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -28987,7 +29019,7 @@
         <v>2892</v>
       </c>
     </row>
-    <row r="92" spans="1:10">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -29019,7 +29051,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="93" spans="1:10">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -29051,7 +29083,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="94" spans="1:10">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -29083,7 +29115,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="95" spans="1:10">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>282</v>
       </c>
@@ -29115,7 +29147,7 @@
         <v>50604</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="14.45" customHeight="1">
+    <row r="96" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -29147,7 +29179,7 @@
         <v>21548</v>
       </c>
     </row>
-    <row r="97" spans="1:10">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>288</v>
       </c>
@@ -29179,7 +29211,7 @@
         <v>11936</v>
       </c>
     </row>
-    <row r="98" spans="1:10">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>368</v>
       </c>
@@ -29211,7 +29243,7 @@
         <v>23896</v>
       </c>
     </row>
-    <row r="99" spans="1:10">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>372</v>
       </c>
@@ -29243,7 +29275,7 @@
         <v>43768</v>
       </c>
     </row>
-    <row r="100" spans="1:10">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>375</v>
       </c>
@@ -29275,7 +29307,7 @@
         <v>191176</v>
       </c>
     </row>
-    <row r="101" spans="1:10">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -29307,7 +29339,7 @@
         <v>12628</v>
       </c>
     </row>
-    <row r="102" spans="1:10">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>381</v>
       </c>
@@ -29339,7 +29371,7 @@
         <v>63484</v>
       </c>
     </row>
-    <row r="103" spans="1:10">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -29371,7 +29403,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="104" spans="1:10">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -29403,7 +29435,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:10">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>390</v>
       </c>
@@ -29433,7 +29465,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="106" spans="1:10">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -29465,7 +29497,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="107" spans="1:10">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -29497,7 +29529,7 @@
         <v>3596</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="14.45" customHeight="1">
+    <row r="108" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>479</v>
       </c>
@@ -29529,7 +29561,7 @@
         <v>18256</v>
       </c>
     </row>
-    <row r="109" spans="1:10">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -29561,7 +29593,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -29593,7 +29625,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="111" spans="1:10">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -29625,7 +29657,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="112" spans="1:10">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -29657,7 +29689,7 @@
         <v>20892</v>
       </c>
     </row>
-    <row r="113" spans="1:10">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>473</v>
       </c>
@@ -29689,7 +29721,7 @@
         <v>28024</v>
       </c>
     </row>
-    <row r="114" spans="1:10">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -29721,7 +29753,7 @@
         <v>121104</v>
       </c>
     </row>
-    <row r="115" spans="1:10">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -29753,7 +29785,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="14.45" customHeight="1">
+    <row r="116" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
@@ -29785,7 +29817,7 @@
         <v>158316</v>
       </c>
     </row>
-    <row r="117" spans="1:10">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -29817,7 +29849,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="118" spans="1:10">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -29849,7 +29881,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="119" spans="1:10">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>228</v>
       </c>
@@ -29881,7 +29913,7 @@
         <v>6552</v>
       </c>
     </row>
-    <row r="120" spans="1:10">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -29913,7 +29945,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:10">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>234</v>
       </c>
@@ -29945,7 +29977,7 @@
         <v>20720</v>
       </c>
     </row>
-    <row r="122" spans="1:10">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -29977,7 +30009,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="14.45" customHeight="1">
+    <row r="123" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>240</v>
       </c>
@@ -30009,7 +30041,7 @@
         <v>3516</v>
       </c>
     </row>
-    <row r="124" spans="1:10">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>243</v>
       </c>
@@ -30041,7 +30073,7 @@
         <v>59652</v>
       </c>
     </row>
-    <row r="125" spans="1:10">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -30073,7 +30105,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="126" spans="1:10">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>295</v>
       </c>
@@ -30105,7 +30137,7 @@
         <v>6572</v>
       </c>
     </row>
-    <row r="127" spans="1:10">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>322</v>
       </c>
@@ -30137,7 +30169,7 @@
         <v>73144</v>
       </c>
     </row>
-    <row r="128" spans="1:10">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -30169,7 +30201,7 @@
         <v>6016</v>
       </c>
     </row>
-    <row r="129" spans="1:10">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>407</v>
       </c>
@@ -30201,7 +30233,7 @@
         <v>66764</v>
       </c>
     </row>
-    <row r="130" spans="1:10">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>411</v>
       </c>
@@ -30233,7 +30265,7 @@
         <v>3928</v>
       </c>
     </row>
-    <row r="131" spans="1:10">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>414</v>
       </c>
@@ -30265,7 +30297,7 @@
         <v>37528</v>
       </c>
     </row>
-    <row r="132" spans="1:10">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>417</v>
       </c>
@@ -30297,7 +30329,7 @@
         <v>77480</v>
       </c>
     </row>
-    <row r="133" spans="1:10">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>420</v>
       </c>
@@ -30329,7 +30361,7 @@
         <v>22252</v>
       </c>
     </row>
-    <row r="134" spans="1:10">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -30361,7 +30393,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="135" spans="1:10">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>426</v>
       </c>
@@ -30393,7 +30425,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="136" spans="1:10">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>429</v>
       </c>
@@ -30425,7 +30457,7 @@
         <v>150540</v>
       </c>
     </row>
-    <row r="137" spans="1:10">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -30457,7 +30489,7 @@
         <v>3432</v>
       </c>
     </row>
-    <row r="138" spans="1:10">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>435</v>
       </c>
@@ -30489,7 +30521,7 @@
         <v>145332</v>
       </c>
     </row>
-    <row r="139" spans="1:10">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>438</v>
       </c>
@@ -30521,7 +30553,7 @@
         <v>97836</v>
       </c>
     </row>
-    <row r="140" spans="1:10">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -30553,7 +30585,7 @@
         <v>20896</v>
       </c>
     </row>
-    <row r="141" spans="1:10">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -30585,7 +30617,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="142" spans="1:10">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -30615,7 +30647,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="143" spans="1:10">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -30647,7 +30679,7 @@
         <v>7356</v>
       </c>
     </row>
-    <row r="144" spans="1:10">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -30833,7 +30865,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037935A5-1106-459B-9A86-1C0042E776B1}">
   <dimension ref="A1:F49"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="29" customWidth="1"/>
     <col min="2" max="2" width="32" style="29" customWidth="1"/>
@@ -30841,629 +30873,629 @@
     <col min="4" max="4" width="54.140625" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
+        <v>704</v>
+      </c>
+      <c r="B1" s="30" t="s">
         <v>628</v>
       </c>
-      <c r="B1" s="30" t="s">
+      <c r="C1" s="30" t="s">
         <v>629</v>
       </c>
-      <c r="C1" s="30" t="s">
+      <c r="D1" s="30" t="s">
         <v>630</v>
       </c>
-      <c r="D1" s="30" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>484</v>
       </c>
       <c r="C2" s="29" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>485</v>
       </c>
       <c r="C3" s="29" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>487</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>488</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>490</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>491</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="40.9" customHeight="1">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>493</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="28.9">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>632</v>
+        <v>703</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>494</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>510</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="D10" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>511</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="D11" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="B12" s="29" t="s">
         <v>512</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D12" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>513</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="D13" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>514</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D14" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="29" t="s">
-        <v>643</v>
+        <v>705</v>
       </c>
       <c r="B15" s="29" t="s">
         <v>515</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D15" s="29" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="43.15">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>518</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="D16" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="28.9">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A17" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>519</v>
       </c>
       <c r="C17" s="31" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="D17" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="43.15">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>520</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="D18" s="31" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="43.15">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>521</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="D19" s="31" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="F19" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="43.15">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>522</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="D20" s="29" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>523</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>661</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>524</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D22" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>525</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="D23" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>526</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="D24" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B25" s="29" t="s">
         <v>527</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="D25" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>528</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="D26" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="28.9">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>530</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="D27" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="43.15">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>532</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="D28" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="43.15">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="29" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>534</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="D29" s="29" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="E29" s="29" t="s">
-        <v>659</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="43.9" customHeight="1">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="29" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="B30" s="29" t="s">
         <v>569</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="D30" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="34.15" customHeight="1">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="29" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="B31" s="29" t="s">
         <v>570</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="D31" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="28.9" customHeight="1">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="29" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>571</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="D32" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="19.149999999999999" customHeight="1">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="29" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>572</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="D33" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="29" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>573</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="D34" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="28.9">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="29" t="s">
-        <v>672</v>
+        <v>707</v>
       </c>
       <c r="B35" s="29" t="s">
         <v>574</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="57.6">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A36" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>575</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D36" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="43.15">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B37" s="29" t="s">
         <v>576</v>
       </c>
       <c r="C37" s="31" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D37" s="31" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="57.6">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="60" x14ac:dyDescent="0.25">
       <c r="A38" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>577</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="D38" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="43.15">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B39" s="29" t="s">
         <v>578</v>
       </c>
       <c r="C39" s="31" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="D39" s="31" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="33" customHeight="1">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B40" s="29" t="s">
         <v>579</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="D40" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="43.15">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A41" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B41" s="29" t="s">
         <v>580</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D41" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="43.15">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A42" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B42" s="29" t="s">
         <v>581</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="D42" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="43.15">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A43" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>582</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="D43" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="43.15">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="29" t="s">
-        <v>679</v>
+        <v>708</v>
       </c>
       <c r="B44" s="29" t="s">
         <v>583</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="D44" s="29" t="s">
-        <v>653</v>
-      </c>
-    </row>
-    <row r="49" spans="4:4">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D49" s="31"/>
     </row>
   </sheetData>
@@ -31477,169 +31509,169 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="243.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" s="36" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/data/20251212-OdonTraits_Europe.xlsx
+++ b/data/20251212-OdonTraits_Europe.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\te19xejy\Documents\local projects\odontraitseurope\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CESAB\Documents\Postdoc\Code\odontraitseurope\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C0F9A82-B8C8-4CE3-982F-A1B756BE880F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="taxonomic" sheetId="2" r:id="rId1"/>
@@ -50,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="709">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4218" uniqueCount="708">
   <si>
     <t>species_name</t>
   </si>
@@ -2015,9 +2014,6 @@
   </si>
   <si>
     <t>end of the main flight period in Europe, excluding the extreme late records</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
   </si>
   <si>
     <t>Species Temperature Index (STI) is the average temperature (°C) of the species’ range in Europe, based on the data from 1990 onwards from the European atlas; uses average monthly temperatures for 1960–1990 (WordlClim) at a 50 × 50 km grid scale.</t>
@@ -2212,7 +2208,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -2476,8 +2472,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal_Sheet1" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_Sheet1" xfId="1"/>
   </cellStyles>
   <dxfs count="29">
     <dxf>
@@ -2726,7 +2722,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -2801,23 +2797,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -2853,23 +2832,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -3045,18 +3007,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E144"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.81640625" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
@@ -3073,7 +3035,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -3090,7 +3052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -3107,7 +3069,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
@@ -3124,7 +3086,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>16</v>
       </c>
@@ -3141,7 +3103,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -3158,7 +3120,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -3175,7 +3137,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -3192,7 +3154,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -3209,7 +3171,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -3226,7 +3188,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -3243,7 +3205,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -3260,7 +3222,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -3277,7 +3239,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -3294,7 +3256,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -3311,7 +3273,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -3328,7 +3290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -3345,7 +3307,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -3362,7 +3324,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
@@ -3379,7 +3341,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>64</v>
       </c>
@@ -3396,7 +3358,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>68</v>
       </c>
@@ -3413,7 +3375,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>73</v>
       </c>
@@ -3430,7 +3392,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>76</v>
       </c>
@@ -3447,7 +3409,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>79</v>
       </c>
@@ -3464,7 +3426,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>82</v>
       </c>
@@ -3481,7 +3443,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>87</v>
       </c>
@@ -3498,7 +3460,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>90</v>
       </c>
@@ -3515,7 +3477,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -3532,7 +3494,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>97</v>
       </c>
@@ -3549,7 +3511,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>100</v>
       </c>
@@ -3566,7 +3528,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>103</v>
       </c>
@@ -3583,7 +3545,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>106</v>
       </c>
@@ -3600,7 +3562,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>109</v>
       </c>
@@ -3617,7 +3579,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>112</v>
       </c>
@@ -3634,7 +3596,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>115</v>
       </c>
@@ -3651,7 +3613,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>118</v>
       </c>
@@ -3668,7 +3630,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>121</v>
       </c>
@@ -3685,7 +3647,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>124</v>
       </c>
@@ -3702,7 +3664,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>127</v>
       </c>
@@ -3719,7 +3681,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>130</v>
       </c>
@@ -3736,7 +3698,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>133</v>
       </c>
@@ -3753,7 +3715,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>136</v>
       </c>
@@ -3770,7 +3732,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>140</v>
       </c>
@@ -3787,7 +3749,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>144</v>
       </c>
@@ -3804,7 +3766,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>147</v>
       </c>
@@ -3821,7 +3783,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>150</v>
       </c>
@@ -3838,7 +3800,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>154</v>
       </c>
@@ -3855,7 +3817,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>157</v>
       </c>
@@ -3872,7 +3834,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>160</v>
       </c>
@@ -3889,7 +3851,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>163</v>
       </c>
@@ -3906,7 +3868,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>166</v>
       </c>
@@ -3923,7 +3885,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>169</v>
       </c>
@@ -3940,7 +3902,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>172</v>
       </c>
@@ -3957,7 +3919,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>175</v>
       </c>
@@ -3974,7 +3936,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>178</v>
       </c>
@@ -3991,7 +3953,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>181</v>
       </c>
@@ -4008,7 +3970,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>185</v>
       </c>
@@ -4025,7 +3987,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>189</v>
       </c>
@@ -4042,7 +4004,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>192</v>
       </c>
@@ -4059,7 +4021,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>197</v>
       </c>
@@ -4076,7 +4038,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>200</v>
       </c>
@@ -4093,7 +4055,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>203</v>
       </c>
@@ -4110,7 +4072,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>206</v>
       </c>
@@ -4127,7 +4089,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>209</v>
       </c>
@@ -4144,7 +4106,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>212</v>
       </c>
@@ -4161,7 +4123,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>215</v>
       </c>
@@ -4178,7 +4140,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>220</v>
       </c>
@@ -4195,7 +4157,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>224</v>
       </c>
@@ -4212,7 +4174,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>228</v>
       </c>
@@ -4229,7 +4191,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>231</v>
       </c>
@@ -4246,7 +4208,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>234</v>
       </c>
@@ -4263,7 +4225,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>237</v>
       </c>
@@ -4280,7 +4242,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>240</v>
       </c>
@@ -4297,7 +4259,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>243</v>
       </c>
@@ -4314,7 +4276,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>246</v>
       </c>
@@ -4331,7 +4293,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>249</v>
       </c>
@@ -4348,7 +4310,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>254</v>
       </c>
@@ -4365,7 +4327,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>259</v>
       </c>
@@ -4382,7 +4344,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>262</v>
       </c>
@@ -4399,7 +4361,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>265</v>
       </c>
@@ -4416,7 +4378,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>268</v>
       </c>
@@ -4433,7 +4395,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>271</v>
       </c>
@@ -4450,7 +4412,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>275</v>
       </c>
@@ -4467,7 +4429,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>279</v>
       </c>
@@ -4484,7 +4446,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>282</v>
       </c>
@@ -4501,7 +4463,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>285</v>
       </c>
@@ -4518,7 +4480,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>288</v>
       </c>
@@ -4535,7 +4497,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>292</v>
       </c>
@@ -4552,7 +4514,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>295</v>
       </c>
@@ -4569,7 +4531,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>299</v>
       </c>
@@ -4586,7 +4548,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>304</v>
       </c>
@@ -4603,7 +4565,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>306</v>
       </c>
@@ -4620,7 +4582,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>310</v>
       </c>
@@ -4637,7 +4599,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>313</v>
       </c>
@@ -4654,7 +4616,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>316</v>
       </c>
@@ -4671,7 +4633,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>319</v>
       </c>
@@ -4688,7 +4650,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>322</v>
       </c>
@@ -4705,7 +4667,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>326</v>
       </c>
@@ -4722,7 +4684,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>329</v>
       </c>
@@ -4739,7 +4701,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>334</v>
       </c>
@@ -4756,7 +4718,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>338</v>
       </c>
@@ -4773,7 +4735,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>342</v>
       </c>
@@ -4790,7 +4752,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>346</v>
       </c>
@@ -4807,7 +4769,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>349</v>
       </c>
@@ -4824,7 +4786,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>352</v>
       </c>
@@ -4841,7 +4803,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>355</v>
       </c>
@@ -4858,7 +4820,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>358</v>
       </c>
@@ -4875,7 +4837,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>362</v>
       </c>
@@ -4892,7 +4854,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>365</v>
       </c>
@@ -4909,7 +4871,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>368</v>
       </c>
@@ -4926,7 +4888,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>372</v>
       </c>
@@ -4943,7 +4905,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>375</v>
       </c>
@@ -4960,7 +4922,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>378</v>
       </c>
@@ -4977,7 +4939,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>381</v>
       </c>
@@ -4994,7 +4956,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>384</v>
       </c>
@@ -5011,7 +4973,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>387</v>
       </c>
@@ -5028,7 +4990,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>390</v>
       </c>
@@ -5045,7 +5007,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>393</v>
       </c>
@@ -5062,7 +5024,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>396</v>
       </c>
@@ -5079,7 +5041,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>399</v>
       </c>
@@ -5096,7 +5058,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>403</v>
       </c>
@@ -5113,7 +5075,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>407</v>
       </c>
@@ -5130,7 +5092,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>411</v>
       </c>
@@ -5147,7 +5109,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>414</v>
       </c>
@@ -5164,7 +5126,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>417</v>
       </c>
@@ -5181,7 +5143,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>420</v>
       </c>
@@ -5198,7 +5160,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>423</v>
       </c>
@@ -5215,7 +5177,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>426</v>
       </c>
@@ -5232,7 +5194,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>429</v>
       </c>
@@ -5249,7 +5211,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>432</v>
       </c>
@@ -5266,7 +5228,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>435</v>
       </c>
@@ -5283,7 +5245,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>438</v>
       </c>
@@ -5300,7 +5262,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>441</v>
       </c>
@@ -5317,7 +5279,7 @@
         <v>444</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>445</v>
       </c>
@@ -5334,7 +5296,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>448</v>
       </c>
@@ -5351,7 +5313,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>451</v>
       </c>
@@ -5368,7 +5330,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>454</v>
       </c>
@@ -5385,7 +5347,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>458</v>
       </c>
@@ -5402,7 +5364,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>463</v>
       </c>
@@ -5419,7 +5381,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>465</v>
       </c>
@@ -5436,7 +5398,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>470</v>
       </c>
@@ -5453,7 +5415,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>473</v>
       </c>
@@ -5470,7 +5432,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>476</v>
       </c>
@@ -5487,7 +5449,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>479</v>
       </c>
@@ -5505,8 +5467,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E144" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E144">
+  <autoFilter ref="A1:E144">
+    <sortState ref="A2:E144">
       <sortCondition ref="C1:C144"/>
     </sortState>
   </autoFilter>
@@ -5516,25 +5478,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L144"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" style="8" customWidth="1"/>
-    <col min="7" max="7" width="4.42578125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="8" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="8" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="8" customWidth="1"/>
-    <col min="11" max="11" width="20.85546875" customWidth="1"/>
-    <col min="12" max="12" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.7265625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="18.54296875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="19.26953125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="4.453125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" style="8" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" style="8" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" style="8" customWidth="1"/>
+    <col min="11" max="11" width="20.81640625" customWidth="1"/>
+    <col min="12" max="12" width="16.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="9" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="9" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -5572,7 +5534,7 @@
         <v>494</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -5610,7 +5572,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -5648,7 +5610,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -5686,7 +5648,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -5724,7 +5686,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -5762,7 +5724,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -5800,7 +5762,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -5838,7 +5800,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -5876,7 +5838,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -5914,7 +5876,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -5952,7 +5914,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -5990,7 +5952,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -6028,7 +5990,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -6066,7 +6028,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -6104,7 +6066,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>50</v>
       </c>
@@ -6142,7 +6104,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>53</v>
       </c>
@@ -6180,7 +6142,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -6218,7 +6180,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -6256,7 +6218,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>60</v>
       </c>
@@ -6294,7 +6256,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -6332,7 +6294,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -6370,7 +6332,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -6408,7 +6370,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -6446,7 +6408,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -6484,7 +6446,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>82</v>
       </c>
@@ -6522,7 +6484,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>87</v>
       </c>
@@ -6560,7 +6522,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>299</v>
       </c>
@@ -6598,7 +6560,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>304</v>
       </c>
@@ -6636,7 +6598,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -6674,7 +6636,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -6712,7 +6674,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -6750,7 +6712,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -6788,7 +6750,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -6826,7 +6788,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>106</v>
       </c>
@@ -6864,7 +6826,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -6902,7 +6864,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>112</v>
       </c>
@@ -6940,7 +6902,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -6978,7 +6940,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>118</v>
       </c>
@@ -7016,7 +6978,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>121</v>
       </c>
@@ -7054,7 +7016,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>124</v>
       </c>
@@ -7092,7 +7054,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>127</v>
       </c>
@@ -7130,7 +7092,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>130</v>
       </c>
@@ -7168,7 +7130,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>133</v>
       </c>
@@ -7206,7 +7168,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>192</v>
       </c>
@@ -7244,7 +7206,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>197</v>
       </c>
@@ -7282,7 +7244,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -7320,7 +7282,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>203</v>
       </c>
@@ -7358,7 +7320,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -7396,7 +7358,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -7434,7 +7396,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -7472,7 +7434,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>215</v>
       </c>
@@ -7510,7 +7472,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>334</v>
       </c>
@@ -7548,7 +7510,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -7586,7 +7548,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>136</v>
       </c>
@@ -7624,7 +7586,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -7662,7 +7624,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>220</v>
       </c>
@@ -7700,7 +7662,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>140</v>
       </c>
@@ -7738,7 +7700,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>144</v>
       </c>
@@ -7776,7 +7738,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>147</v>
       </c>
@@ -7814,7 +7776,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -7852,7 +7814,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>259</v>
       </c>
@@ -7890,7 +7852,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -7928,7 +7890,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -7966,7 +7928,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>268</v>
       </c>
@@ -8004,7 +7966,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -8042,7 +8004,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>154</v>
       </c>
@@ -8080,7 +8042,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -8118,7 +8080,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -8156,7 +8118,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -8194,7 +8156,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -8232,7 +8194,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -8270,7 +8232,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>172</v>
       </c>
@@ -8308,7 +8270,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -8346,7 +8308,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -8384,7 +8346,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>306</v>
       </c>
@@ -8422,7 +8384,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -8460,7 +8422,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>313</v>
       </c>
@@ -8498,7 +8460,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>316</v>
       </c>
@@ -8536,7 +8498,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>319</v>
       </c>
@@ -8574,7 +8536,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>342</v>
       </c>
@@ -8612,7 +8574,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>346</v>
       </c>
@@ -8650,7 +8612,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>349</v>
       </c>
@@ -8688,7 +8650,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>507</v>
       </c>
@@ -8726,7 +8688,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>355</v>
       </c>
@@ -8764,7 +8726,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>358</v>
       </c>
@@ -8802,7 +8764,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>362</v>
       </c>
@@ -8840,7 +8802,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>365</v>
       </c>
@@ -8878,7 +8840,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -8916,7 +8878,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -8954,7 +8916,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -8992,7 +8954,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>181</v>
       </c>
@@ -9030,7 +8992,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -9068,7 +9030,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -9106,7 +9068,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>282</v>
       </c>
@@ -9144,7 +9106,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -9182,7 +9144,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>288</v>
       </c>
@@ -9220,7 +9182,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>368</v>
       </c>
@@ -9258,7 +9220,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>372</v>
       </c>
@@ -9296,7 +9258,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>375</v>
       </c>
@@ -9334,7 +9296,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -9372,7 +9334,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>381</v>
       </c>
@@ -9410,7 +9372,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -9448,7 +9410,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -9486,7 +9448,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>390</v>
       </c>
@@ -9524,7 +9486,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -9562,7 +9524,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -9600,7 +9562,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>479</v>
       </c>
@@ -9638,7 +9600,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -9676,7 +9638,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -9714,7 +9676,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -9752,7 +9714,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -9790,7 +9752,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>473</v>
       </c>
@@ -9828,7 +9790,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -9866,7 +9828,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -9904,7 +9866,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>189</v>
       </c>
@@ -9942,7 +9904,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -9980,7 +9942,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>224</v>
       </c>
@@ -10018,7 +9980,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>228</v>
       </c>
@@ -10056,7 +10018,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -10094,7 +10056,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
         <v>234</v>
       </c>
@@ -10132,7 +10094,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -10170,7 +10132,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
         <v>240</v>
       </c>
@@ -10208,7 +10170,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>243</v>
       </c>
@@ -10246,7 +10208,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -10284,7 +10246,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>295</v>
       </c>
@@ -10322,7 +10284,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>322</v>
       </c>
@@ -10360,7 +10322,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>326</v>
       </c>
@@ -10398,7 +10360,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
         <v>407</v>
       </c>
@@ -10436,7 +10398,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>411</v>
       </c>
@@ -10474,7 +10436,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>414</v>
       </c>
@@ -10512,7 +10474,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>417</v>
       </c>
@@ -10550,7 +10512,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>420</v>
       </c>
@@ -10588,7 +10550,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -10626,7 +10588,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>426</v>
       </c>
@@ -10664,7 +10626,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>429</v>
       </c>
@@ -10702,7 +10664,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -10740,7 +10702,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>435</v>
       </c>
@@ -10778,7 +10740,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
         <v>438</v>
       </c>
@@ -10816,7 +10778,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -10854,7 +10816,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -10892,7 +10854,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -10930,7 +10892,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -10968,7 +10930,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -11007,8 +10969,8 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L144" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L144">
+  <autoFilter ref="A1:L144">
+    <sortState ref="A2:L144">
       <sortCondition ref="A1:A134"/>
     </sortState>
   </autoFilter>
@@ -11017,19 +10979,19 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G146"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.28515625" customWidth="1"/>
-    <col min="2" max="3" width="16.85546875" style="8" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" style="8" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="8" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="24.85546875" style="8" customWidth="1"/>
+    <col min="1" max="1" width="35.26953125" customWidth="1"/>
+    <col min="2" max="3" width="16.81640625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="16.7265625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" style="8" customWidth="1"/>
+    <col min="6" max="6" width="12.453125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="24.81640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -11052,7 +11014,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -11075,7 +11037,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -11098,7 +11060,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -11121,7 +11083,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -11144,7 +11106,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -11167,7 +11129,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -11190,7 +11152,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -11213,7 +11175,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -11236,7 +11198,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -11259,7 +11221,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -11282,7 +11244,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -11305,7 +11267,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -11328,7 +11290,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -11351,7 +11313,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -11374,7 +11336,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -11397,7 +11359,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -11420,7 +11382,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -11443,7 +11405,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -11466,7 +11428,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>60</v>
       </c>
@@ -11489,7 +11451,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -11512,7 +11474,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -11537,7 +11499,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -11562,7 +11524,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -11587,7 +11549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -11612,7 +11574,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -11635,7 +11597,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -11660,7 +11622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>299</v>
       </c>
@@ -11685,7 +11647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>304</v>
       </c>
@@ -11710,7 +11672,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -11735,7 +11697,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -11760,7 +11722,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>517</v>
       </c>
@@ -11785,7 +11747,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -11808,7 +11770,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -11831,7 +11793,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
@@ -11856,7 +11818,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -11881,7 +11843,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -11906,7 +11868,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -11931,7 +11893,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -11956,7 +11918,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
@@ -11981,7 +11943,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -12006,7 +11968,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -12031,7 +11993,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -12056,7 +12018,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
@@ -12081,7 +12043,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>192</v>
       </c>
@@ -12104,7 +12066,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
@@ -12127,7 +12089,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -12150,7 +12112,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>203</v>
       </c>
@@ -12173,7 +12135,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -12196,7 +12158,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -12219,7 +12181,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -12242,7 +12204,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>215</v>
       </c>
@@ -12265,7 +12227,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>334</v>
       </c>
@@ -12288,7 +12250,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -12311,7 +12273,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -12336,7 +12298,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -12361,7 +12323,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>220</v>
       </c>
@@ -12384,7 +12346,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>140</v>
       </c>
@@ -12409,7 +12371,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>144</v>
       </c>
@@ -12434,7 +12396,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>147</v>
       </c>
@@ -12459,7 +12421,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -12482,7 +12444,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>259</v>
       </c>
@@ -12505,7 +12467,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -12528,7 +12490,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -12551,7 +12513,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>268</v>
       </c>
@@ -12574,7 +12536,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -12597,7 +12559,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -12622,7 +12584,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -12647,7 +12609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -12672,7 +12634,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -12697,7 +12659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -12720,7 +12682,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -12743,7 +12705,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
@@ -12768,7 +12730,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -12791,7 +12753,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -12814,7 +12776,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>306</v>
       </c>
@@ -12839,7 +12801,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>310</v>
       </c>
@@ -12864,7 +12826,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>313</v>
       </c>
@@ -12889,7 +12851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>316</v>
       </c>
@@ -12914,7 +12876,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>319</v>
       </c>
@@ -12939,7 +12901,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>342</v>
       </c>
@@ -12962,7 +12924,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>346</v>
       </c>
@@ -12985,7 +12947,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>349</v>
       </c>
@@ -13008,7 +12970,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -13031,7 +12993,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
@@ -13054,7 +13016,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>358</v>
       </c>
@@ -13077,7 +13039,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -13100,7 +13062,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>365</v>
       </c>
@@ -13123,7 +13085,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -13146,7 +13108,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -13169,7 +13131,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -13192,7 +13154,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -13217,7 +13179,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -13240,7 +13202,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -13263,7 +13225,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>282</v>
       </c>
@@ -13286,7 +13248,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -13309,7 +13271,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>288</v>
       </c>
@@ -13332,7 +13294,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>368</v>
       </c>
@@ -13355,7 +13317,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>372</v>
       </c>
@@ -13378,7 +13340,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>375</v>
       </c>
@@ -13401,7 +13363,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -13424,7 +13386,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>381</v>
       </c>
@@ -13447,7 +13409,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -13470,7 +13432,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -13493,7 +13455,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>390</v>
       </c>
@@ -13516,7 +13478,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -13539,7 +13501,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -13562,7 +13524,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>479</v>
       </c>
@@ -13585,7 +13547,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -13608,7 +13570,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -13631,7 +13593,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -13656,7 +13618,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -13681,7 +13643,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>473</v>
       </c>
@@ -13706,7 +13668,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -13729,7 +13691,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -13752,7 +13714,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
@@ -13777,7 +13739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -13800,7 +13762,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -13823,7 +13785,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>228</v>
       </c>
@@ -13846,7 +13808,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -13869,7 +13831,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>234</v>
       </c>
@@ -13892,7 +13854,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -13915,7 +13877,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>240</v>
       </c>
@@ -13938,7 +13900,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>243</v>
       </c>
@@ -13961,7 +13923,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -13984,7 +13946,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>295</v>
       </c>
@@ -14007,7 +13969,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>322</v>
       </c>
@@ -14032,7 +13994,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -14057,7 +14019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>407</v>
       </c>
@@ -14080,7 +14042,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>411</v>
       </c>
@@ -14103,7 +14065,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>414</v>
       </c>
@@ -14126,7 +14088,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>417</v>
       </c>
@@ -14149,7 +14111,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>420</v>
       </c>
@@ -14172,7 +14134,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -14195,7 +14157,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>426</v>
       </c>
@@ -14218,7 +14180,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>429</v>
       </c>
@@ -14241,7 +14203,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -14264,7 +14226,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>435</v>
       </c>
@@ -14287,7 +14249,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>438</v>
       </c>
@@ -14310,7 +14272,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -14333,7 +14295,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -14356,7 +14318,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -14379,7 +14341,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -14402,7 +14364,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -14425,15 +14387,15 @@
         <v>516</v>
       </c>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A145" s="1"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A146" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G146" xr:uid="{00000000-0009-0000-0000-000004000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G146">
+  <autoFilter ref="A1:G146">
+    <sortState ref="A2:G146">
       <sortCondition ref="A1:A146"/>
     </sortState>
   </autoFilter>
@@ -14442,28 +14404,28 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R181"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" customWidth="1"/>
+    <col min="1" max="1" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7265625" style="10" customWidth="1"/>
+    <col min="4" max="4" width="9.26953125" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.28515625" customWidth="1"/>
-    <col min="13" max="13" width="10.140625" customWidth="1"/>
-    <col min="14" max="14" width="18.28515625" customWidth="1"/>
-    <col min="15" max="15" width="6.5703125" customWidth="1"/>
-    <col min="16" max="16" width="15.7109375" customWidth="1"/>
-    <col min="17" max="17" width="6.140625" customWidth="1"/>
-    <col min="18" max="18" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.54296875" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" customWidth="1"/>
+    <col min="11" max="11" width="8.7265625" customWidth="1"/>
+    <col min="12" max="12" width="11.26953125" customWidth="1"/>
+    <col min="13" max="13" width="10.1796875" customWidth="1"/>
+    <col min="14" max="14" width="18.26953125" customWidth="1"/>
+    <col min="15" max="15" width="6.54296875" customWidth="1"/>
+    <col min="16" max="16" width="15.7265625" customWidth="1"/>
+    <col min="17" max="17" width="6.1796875" customWidth="1"/>
+    <col min="18" max="18" width="15.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -14519,7 +14481,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>5</v>
       </c>
@@ -14575,7 +14537,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -14631,7 +14593,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -14687,7 +14649,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -14743,7 +14705,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -14799,7 +14761,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -14855,7 +14817,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -14911,7 +14873,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -14967,7 +14929,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -15023,7 +14985,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -15079,7 +15041,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -15135,7 +15097,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -15191,7 +15153,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>44</v>
       </c>
@@ -15247,7 +15209,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -15303,7 +15265,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>50</v>
       </c>
@@ -15359,7 +15321,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" s="10" t="s">
         <v>53</v>
       </c>
@@ -15415,7 +15377,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>57</v>
       </c>
@@ -15471,7 +15433,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -15527,7 +15489,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>60</v>
       </c>
@@ -15583,7 +15545,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -15639,7 +15601,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -15695,7 +15657,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>73</v>
       </c>
@@ -15751,7 +15713,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -15807,7 +15769,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -15863,7 +15825,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>82</v>
       </c>
@@ -15919,7 +15881,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" s="10" t="s">
         <v>87</v>
       </c>
@@ -15975,7 +15937,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>299</v>
       </c>
@@ -16031,7 +15993,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>304</v>
       </c>
@@ -16087,7 +16049,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>90</v>
       </c>
@@ -16143,7 +16105,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -16199,7 +16161,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>97</v>
       </c>
@@ -16255,7 +16217,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -16311,7 +16273,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -16367,7 +16329,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" s="10" t="s">
         <v>106</v>
       </c>
@@ -16423,7 +16385,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -16479,7 +16441,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" s="10" t="s">
         <v>112</v>
       </c>
@@ -16535,7 +16497,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -16591,7 +16553,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" s="10" t="s">
         <v>118</v>
       </c>
@@ -16647,7 +16609,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>121</v>
       </c>
@@ -16703,7 +16665,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" s="10" t="s">
         <v>124</v>
       </c>
@@ -16759,7 +16721,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>127</v>
       </c>
@@ -16815,7 +16777,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" s="10" t="s">
         <v>130</v>
       </c>
@@ -16871,7 +16833,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>133</v>
       </c>
@@ -16927,7 +16889,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" s="10" t="s">
         <v>192</v>
       </c>
@@ -16983,7 +16945,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>197</v>
       </c>
@@ -17039,7 +17001,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -17095,7 +17057,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>203</v>
       </c>
@@ -17151,7 +17113,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -17207,7 +17169,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -17263,7 +17225,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -17319,7 +17281,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>215</v>
       </c>
@@ -17375,7 +17337,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" s="10" t="s">
         <v>334</v>
       </c>
@@ -17431,7 +17393,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -17487,7 +17449,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" s="10" t="s">
         <v>136</v>
       </c>
@@ -17543,7 +17505,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -17599,7 +17561,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" s="10" t="s">
         <v>220</v>
       </c>
@@ -17655,7 +17617,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>140</v>
       </c>
@@ -17711,7 +17673,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" s="10" t="s">
         <v>144</v>
       </c>
@@ -17767,7 +17729,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>147</v>
       </c>
@@ -17823,7 +17785,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -17879,7 +17841,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>259</v>
       </c>
@@ -17935,7 +17897,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -17991,7 +17953,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -18047,7 +18009,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" s="10" t="s">
         <v>268</v>
       </c>
@@ -18103,7 +18065,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -18159,7 +18121,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>154</v>
       </c>
@@ -18215,7 +18177,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>157</v>
       </c>
@@ -18271,7 +18233,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -18327,7 +18289,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -18383,7 +18345,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>166</v>
       </c>
@@ -18439,7 +18401,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -18495,7 +18457,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>172</v>
       </c>
@@ -18551,7 +18513,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -18607,7 +18569,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -18663,7 +18625,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>306</v>
       </c>
@@ -18719,7 +18681,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>310</v>
       </c>
@@ -18775,7 +18737,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>313</v>
       </c>
@@ -18831,7 +18793,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" s="10" t="s">
         <v>316</v>
       </c>
@@ -18887,7 +18849,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>319</v>
       </c>
@@ -18943,7 +18905,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" s="10" t="s">
         <v>342</v>
       </c>
@@ -18999,7 +18961,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>346</v>
       </c>
@@ -19055,7 +19017,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" s="10" t="s">
         <v>349</v>
       </c>
@@ -19111,7 +19073,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>507</v>
       </c>
@@ -19167,7 +19129,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A85" s="10" t="s">
         <v>355</v>
       </c>
@@ -19223,7 +19185,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>358</v>
       </c>
@@ -19279,7 +19241,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A87" s="10" t="s">
         <v>362</v>
       </c>
@@ -19335,7 +19297,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>365</v>
       </c>
@@ -19391,7 +19353,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -19447,7 +19409,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -19503,7 +19465,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -19559,7 +19521,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>181</v>
       </c>
@@ -19615,7 +19577,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -19671,7 +19633,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -19727,7 +19689,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A95" s="10" t="s">
         <v>282</v>
       </c>
@@ -19783,7 +19745,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -19839,7 +19801,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A97" s="10" t="s">
         <v>288</v>
       </c>
@@ -19895,7 +19857,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>368</v>
       </c>
@@ -19951,7 +19913,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" s="10" t="s">
         <v>372</v>
       </c>
@@ -20007,7 +19969,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>375</v>
       </c>
@@ -20063,7 +20025,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -20119,7 +20081,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>381</v>
       </c>
@@ -20175,7 +20137,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -20231,7 +20193,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -20287,7 +20249,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>390</v>
       </c>
@@ -20343,7 +20305,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -20399,7 +20361,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -20455,7 +20417,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>479</v>
       </c>
@@ -20511,7 +20473,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -20567,7 +20529,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -20623,7 +20585,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -20679,7 +20641,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -20735,7 +20697,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A113" s="10" t="s">
         <v>473</v>
       </c>
@@ -20791,7 +20753,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -20847,7 +20809,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -20903,7 +20865,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>189</v>
       </c>
@@ -20959,7 +20921,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -21015,7 +20977,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>224</v>
       </c>
@@ -21071,7 +21033,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A119" s="10" t="s">
         <v>228</v>
       </c>
@@ -21127,7 +21089,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -21183,7 +21145,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A121" s="10" t="s">
         <v>234</v>
       </c>
@@ -21239,7 +21201,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -21295,7 +21257,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A123" s="10" t="s">
         <v>240</v>
       </c>
@@ -21351,7 +21313,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>243</v>
       </c>
@@ -21407,7 +21369,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -21463,7 +21425,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>295</v>
       </c>
@@ -21519,7 +21481,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A127" s="10" t="s">
         <v>322</v>
       </c>
@@ -21575,7 +21537,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>326</v>
       </c>
@@ -21631,7 +21593,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A129" s="10" t="s">
         <v>407</v>
       </c>
@@ -21687,7 +21649,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>411</v>
       </c>
@@ -21743,7 +21705,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A131" s="10" t="s">
         <v>414</v>
       </c>
@@ -21799,7 +21761,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>417</v>
       </c>
@@ -21855,7 +21817,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A133" s="10" t="s">
         <v>420</v>
       </c>
@@ -21911,7 +21873,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -21967,7 +21929,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A135" s="10" t="s">
         <v>426</v>
       </c>
@@ -22023,7 +21985,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>429</v>
       </c>
@@ -22079,7 +22041,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -22135,7 +22097,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>435</v>
       </c>
@@ -22191,7 +22153,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A139" s="10" t="s">
         <v>438</v>
       </c>
@@ -22247,7 +22209,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -22303,7 +22265,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -22359,7 +22321,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -22415,7 +22377,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -22471,7 +22433,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -22527,139 +22489,139 @@
         <v>557</v>
       </c>
     </row>
-    <row r="145" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B145" s="1"/>
     </row>
-    <row r="146" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B146" s="1"/>
     </row>
-    <row r="147" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B147" s="1"/>
     </row>
-    <row r="148" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B148" s="1"/>
     </row>
-    <row r="149" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B149" s="1"/>
     </row>
-    <row r="150" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B150" s="1"/>
     </row>
-    <row r="151" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B151" s="1"/>
     </row>
-    <row r="152" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B152" s="1"/>
     </row>
-    <row r="153" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B153" s="1"/>
     </row>
-    <row r="154" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B154" s="1"/>
     </row>
-    <row r="155" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B155" s="1"/>
     </row>
-    <row r="156" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B156" s="1"/>
     </row>
-    <row r="157" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B157" s="1"/>
     </row>
-    <row r="158" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B158" s="1"/>
     </row>
-    <row r="159" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B159" s="1"/>
     </row>
-    <row r="160" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B160" s="1"/>
     </row>
-    <row r="161" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B161" s="1"/>
     </row>
-    <row r="162" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B162" s="1"/>
     </row>
-    <row r="163" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B163" s="1"/>
     </row>
-    <row r="164" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B164" s="1"/>
     </row>
-    <row r="165" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B165" s="1"/>
     </row>
-    <row r="166" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B166" s="1"/>
     </row>
-    <row r="167" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B167" s="1"/>
     </row>
-    <row r="168" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B168" s="1"/>
     </row>
-    <row r="169" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B169" s="1"/>
     </row>
-    <row r="170" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B170" s="1"/>
     </row>
-    <row r="171" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B171" s="1"/>
     </row>
-    <row r="172" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B172" s="1"/>
     </row>
-    <row r="173" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B173" s="1"/>
     </row>
-    <row r="174" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B174" s="1"/>
     </row>
-    <row r="175" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B175" s="1"/>
     </row>
-    <row r="176" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B176" s="1"/>
     </row>
-    <row r="177" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B177" s="1"/>
     </row>
-    <row r="178" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B178" s="1"/>
     </row>
-    <row r="179" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B179" s="1"/>
     </row>
-    <row r="180" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B180" s="1"/>
     </row>
-    <row r="181" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B181" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R181" xr:uid="{00000000-0001-0000-0500-000000000000}"/>
+  <autoFilter ref="A1:R181"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:P144"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.85546875" style="7" customWidth="1"/>
-    <col min="3" max="4" width="16.42578125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="8.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
+    <col min="1" max="1" width="25.81640625" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" style="7" customWidth="1"/>
+    <col min="3" max="4" width="16.453125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="8.453125" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.1796875" style="7" customWidth="1"/>
+    <col min="11" max="11" width="22.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -22682,7 +22644,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -22705,7 +22667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -22728,7 +22690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -22751,7 +22713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -22774,7 +22736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -22797,7 +22759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -22824,7 +22786,7 @@
       <c r="M7" s="14"/>
       <c r="N7" s="15"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -22851,7 +22813,7 @@
       <c r="M8" s="16"/>
       <c r="N8" s="15"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -22878,7 +22840,7 @@
       <c r="M9" s="18"/>
       <c r="N9" s="15"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -22905,7 +22867,7 @@
       <c r="M10" s="16"/>
       <c r="N10" s="17"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -22932,7 +22894,7 @@
       <c r="M11" s="16"/>
       <c r="N11" s="15"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -22955,7 +22917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -22978,7 +22940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -23001,7 +22963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -23024,7 +22986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -23047,7 +23009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -23070,7 +23032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -23093,7 +23055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -23116,7 +23078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>60</v>
       </c>
@@ -23139,7 +23101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -23162,7 +23124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -23185,7 +23147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -23208,7 +23170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -23231,7 +23193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -23254,7 +23216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -23277,7 +23239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -23300,7 +23262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>299</v>
       </c>
@@ -23323,7 +23285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>304</v>
       </c>
@@ -23346,7 +23308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -23369,7 +23331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -23392,7 +23354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
@@ -23415,7 +23377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -23438,7 +23400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -23461,7 +23423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
@@ -23484,7 +23446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -23507,7 +23469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -23530,7 +23492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -23553,7 +23515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -23576,7 +23538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
@@ -23599,7 +23561,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -23622,7 +23584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -23645,7 +23607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -23668,7 +23630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
@@ -23691,7 +23653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>192</v>
       </c>
@@ -23714,7 +23676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
@@ -23737,7 +23699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -23760,7 +23722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>203</v>
       </c>
@@ -23783,7 +23745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -23806,7 +23768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -23829,7 +23791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -23852,7 +23814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>215</v>
       </c>
@@ -23875,7 +23837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>334</v>
       </c>
@@ -23898,7 +23860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -23921,7 +23883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -23944,7 +23906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -23967,7 +23929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>220</v>
       </c>
@@ -23990,7 +23952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>140</v>
       </c>
@@ -24013,7 +23975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>144</v>
       </c>
@@ -24036,7 +23998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>147</v>
       </c>
@@ -24059,7 +24021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -24086,7 +24048,7 @@
       <c r="M61" s="16"/>
       <c r="N61" s="15"/>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>259</v>
       </c>
@@ -24113,7 +24075,7 @@
       <c r="M62" s="16"/>
       <c r="N62" s="15"/>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -24140,7 +24102,7 @@
       <c r="M63" s="16"/>
       <c r="N63" s="15"/>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -24167,7 +24129,7 @@
       <c r="M64" s="16"/>
       <c r="N64" s="15"/>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>268</v>
       </c>
@@ -24194,7 +24156,7 @@
       <c r="M65" s="16"/>
       <c r="N65" s="15"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -24221,7 +24183,7 @@
       <c r="M66" s="16"/>
       <c r="N66" s="15"/>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -24248,7 +24210,7 @@
       <c r="M67" s="16"/>
       <c r="N67" s="15"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>157</v>
       </c>
@@ -24275,7 +24237,7 @@
       <c r="M68" s="16"/>
       <c r="N68" s="15"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -24302,7 +24264,7 @@
       <c r="M69" s="16"/>
       <c r="N69" s="15"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -24329,7 +24291,7 @@
       <c r="M70" s="16"/>
       <c r="N70" s="15"/>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>166</v>
       </c>
@@ -24356,7 +24318,7 @@
       <c r="M71" s="16"/>
       <c r="N71" s="15"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -24383,7 +24345,7 @@
       <c r="M72" s="16"/>
       <c r="N72" s="15"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
@@ -24410,7 +24372,7 @@
       <c r="M73" s="16"/>
       <c r="N73" s="15"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -24437,7 +24399,7 @@
       <c r="M74" s="16"/>
       <c r="N74" s="15"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -24464,7 +24426,7 @@
       <c r="M75" s="16"/>
       <c r="N75" s="15"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>306</v>
       </c>
@@ -24491,7 +24453,7 @@
       <c r="M76" s="16"/>
       <c r="N76" s="15"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>310</v>
       </c>
@@ -24518,7 +24480,7 @@
       <c r="M77" s="16"/>
       <c r="N77" s="15"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>313</v>
       </c>
@@ -24542,7 +24504,7 @@
       </c>
       <c r="N78" s="15"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>316</v>
       </c>
@@ -24569,7 +24531,7 @@
       <c r="M79" s="16"/>
       <c r="N79" s="15"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>319</v>
       </c>
@@ -24596,7 +24558,7 @@
       <c r="M80" s="16"/>
       <c r="N80" s="15"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>342</v>
       </c>
@@ -24623,7 +24585,7 @@
       <c r="M81" s="16"/>
       <c r="N81" s="15"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>346</v>
       </c>
@@ -24650,7 +24612,7 @@
       <c r="M82" s="16"/>
       <c r="N82" s="15"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>349</v>
       </c>
@@ -24677,7 +24639,7 @@
       <c r="M83" s="16"/>
       <c r="N83" s="15"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -24704,7 +24666,7 @@
       <c r="M84" s="16"/>
       <c r="N84" s="15"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
@@ -24731,7 +24693,7 @@
       <c r="M85" s="16"/>
       <c r="N85" s="15"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>358</v>
       </c>
@@ -24754,7 +24716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -24777,7 +24739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>365</v>
       </c>
@@ -24800,7 +24762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -24823,7 +24785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -24846,7 +24808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -24869,7 +24831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -24892,7 +24854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -24915,7 +24877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -24938,7 +24900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>282</v>
       </c>
@@ -24961,7 +24923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -24984,7 +24946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>288</v>
       </c>
@@ -25007,7 +24969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>368</v>
       </c>
@@ -25030,7 +24992,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>372</v>
       </c>
@@ -25053,7 +25015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>375</v>
       </c>
@@ -25076,7 +25038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -25099,7 +25061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>381</v>
       </c>
@@ -25122,7 +25084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -25145,7 +25107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -25168,7 +25130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>390</v>
       </c>
@@ -25191,7 +25153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -25214,7 +25176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -25237,7 +25199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>479</v>
       </c>
@@ -25260,7 +25222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -25283,7 +25245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -25306,7 +25268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -25329,7 +25291,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -25352,7 +25314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>473</v>
       </c>
@@ -25375,7 +25337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -25398,7 +25360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -25421,7 +25383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
@@ -25444,7 +25406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -25467,7 +25429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -25490,7 +25452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>228</v>
       </c>
@@ -25513,7 +25475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -25536,7 +25498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>234</v>
       </c>
@@ -25559,7 +25521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -25582,7 +25544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>240</v>
       </c>
@@ -25605,7 +25567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>243</v>
       </c>
@@ -25628,7 +25590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -25651,7 +25613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>295</v>
       </c>
@@ -25674,7 +25636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>322</v>
       </c>
@@ -25697,7 +25659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -25720,7 +25682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>407</v>
       </c>
@@ -25743,7 +25705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>411</v>
       </c>
@@ -25766,7 +25728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>414</v>
       </c>
@@ -25789,7 +25751,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>417</v>
       </c>
@@ -25812,7 +25774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>420</v>
       </c>
@@ -25835,7 +25797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -25858,7 +25820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>426</v>
       </c>
@@ -25881,7 +25843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>429</v>
       </c>
@@ -25904,7 +25866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -25930,7 +25892,7 @@
       <c r="O137" s="15"/>
       <c r="P137" s="16"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>435</v>
       </c>
@@ -25953,7 +25915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>438</v>
       </c>
@@ -25976,7 +25938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -25999,7 +25961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -26022,7 +25984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -26045,7 +26007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -26068,7 +26030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -26092,24 +26054,24 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G144" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
+  <autoFilter ref="A1:G144"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J144"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="21.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.28515625" customWidth="1"/>
-    <col min="4" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="10" width="18.7109375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="21.7265625" customWidth="1"/>
+    <col min="2" max="2" width="23.7265625" style="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" customWidth="1"/>
+    <col min="4" max="6" width="18.7265625" customWidth="1"/>
+    <col min="7" max="10" width="18.7265625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="22.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -26141,7 +26103,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -26171,7 +26133,7 @@
         <v>25288</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -26203,7 +26165,7 @@
         <v>4512</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>13</v>
       </c>
@@ -26235,7 +26197,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>16</v>
       </c>
@@ -26267,7 +26229,7 @@
         <v>147076</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>19</v>
       </c>
@@ -26299,7 +26261,7 @@
         <v>106576</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>22</v>
       </c>
@@ -26331,7 +26293,7 @@
         <v>57176</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
@@ -26363,7 +26325,7 @@
         <v>37912</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>28</v>
       </c>
@@ -26395,7 +26357,7 @@
         <v>138608</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>31</v>
       </c>
@@ -26427,7 +26389,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
@@ -26459,7 +26421,7 @@
         <v>5712</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>37</v>
       </c>
@@ -26491,7 +26453,7 @@
         <v>6528</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -26523,7 +26485,7 @@
         <v>10784</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>44</v>
       </c>
@@ -26555,7 +26517,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>47</v>
       </c>
@@ -26587,7 +26549,7 @@
         <v>195096</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>50</v>
       </c>
@@ -26619,7 +26581,7 @@
         <v>38224</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>53</v>
       </c>
@@ -26651,7 +26613,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>57</v>
       </c>
@@ -26683,7 +26645,7 @@
         <v>28388</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>329</v>
       </c>
@@ -26715,7 +26677,7 @@
         <v>4784</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>60</v>
       </c>
@@ -26747,7 +26709,7 @@
         <v>62592</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>64</v>
       </c>
@@ -26779,7 +26741,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>68</v>
       </c>
@@ -26811,7 +26773,7 @@
         <v>27532</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>73</v>
       </c>
@@ -26843,7 +26805,7 @@
         <v>129388</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>76</v>
       </c>
@@ -26875,7 +26837,7 @@
         <v>126700</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>79</v>
       </c>
@@ -26907,7 +26869,7 @@
         <v>19516</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>82</v>
       </c>
@@ -26939,7 +26901,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>87</v>
       </c>
@@ -26971,7 +26933,7 @@
         <v>41284</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>299</v>
       </c>
@@ -27003,7 +26965,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>304</v>
       </c>
@@ -27035,7 +26997,7 @@
         <v>119388</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>90</v>
       </c>
@@ -27067,7 +27029,7 @@
         <v>2444</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>94</v>
       </c>
@@ -27099,7 +27061,7 @@
         <v>4080</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>97</v>
       </c>
@@ -27131,7 +27093,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>100</v>
       </c>
@@ -27163,7 +27125,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>103</v>
       </c>
@@ -27195,7 +27157,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>106</v>
       </c>
@@ -27227,7 +27189,7 @@
         <v>30076</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>109</v>
       </c>
@@ -27259,7 +27221,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>112</v>
       </c>
@@ -27291,7 +27253,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>115</v>
       </c>
@@ -27323,7 +27285,7 @@
         <v>3256</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>118</v>
       </c>
@@ -27355,7 +27317,7 @@
         <v>8324</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>121</v>
       </c>
@@ -27387,7 +27349,7 @@
         <v>30920</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -27419,7 +27381,7 @@
         <v>3376</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -27451,7 +27413,7 @@
         <v>182600</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -27483,7 +27445,7 @@
         <v>80984</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>133</v>
       </c>
@@ -27515,7 +27477,7 @@
         <v>25232</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>192</v>
       </c>
@@ -27547,7 +27509,7 @@
         <v>9804</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>197</v>
       </c>
@@ -27579,7 +27541,7 @@
         <v>64768</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>200</v>
       </c>
@@ -27611,7 +27573,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>203</v>
       </c>
@@ -27643,7 +27605,7 @@
         <v>4796</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>206</v>
       </c>
@@ -27675,7 +27637,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>209</v>
       </c>
@@ -27707,7 +27669,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>212</v>
       </c>
@@ -27739,7 +27701,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>215</v>
       </c>
@@ -27771,7 +27733,7 @@
         <v>94976</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>334</v>
       </c>
@@ -27803,7 +27765,7 @@
         <v>88892</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>338</v>
       </c>
@@ -27835,7 +27797,7 @@
         <v>2032</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>136</v>
       </c>
@@ -27867,7 +27829,7 @@
         <v>149804</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>249</v>
       </c>
@@ -27899,7 +27861,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>220</v>
       </c>
@@ -27931,7 +27893,7 @@
         <v>7776</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>140</v>
       </c>
@@ -27963,7 +27925,7 @@
         <v>55688</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>144</v>
       </c>
@@ -27995,7 +27957,7 @@
         <v>91276</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>147</v>
       </c>
@@ -28027,7 +27989,7 @@
         <v>73244</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>254</v>
       </c>
@@ -28059,7 +28021,7 @@
         <v>5100</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>259</v>
       </c>
@@ -28091,7 +28053,7 @@
         <v>42320</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>262</v>
       </c>
@@ -28123,7 +28085,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>265</v>
       </c>
@@ -28155,7 +28117,7 @@
         <v>8564</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>268</v>
       </c>
@@ -28187,7 +28149,7 @@
         <v>32848</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>150</v>
       </c>
@@ -28219,7 +28181,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>154</v>
       </c>
@@ -28251,7 +28213,7 @@
         <v>227176</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>157</v>
       </c>
@@ -28283,7 +28245,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>160</v>
       </c>
@@ -28315,7 +28277,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>163</v>
       </c>
@@ -28347,7 +28309,7 @@
         <v>25824</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>166</v>
       </c>
@@ -28379,7 +28341,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>169</v>
       </c>
@@ -28411,7 +28373,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>172</v>
       </c>
@@ -28443,7 +28405,7 @@
         <v>47244</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>175</v>
       </c>
@@ -28475,7 +28437,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>178</v>
       </c>
@@ -28507,7 +28469,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>306</v>
       </c>
@@ -28539,7 +28501,7 @@
         <v>34392</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>310</v>
       </c>
@@ -28571,7 +28533,7 @@
         <v>32772</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>313</v>
       </c>
@@ -28603,7 +28565,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>316</v>
       </c>
@@ -28635,7 +28597,7 @@
         <v>88524</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>319</v>
       </c>
@@ -28667,7 +28629,7 @@
         <v>41020</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>342</v>
       </c>
@@ -28699,7 +28661,7 @@
         <v>7848</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>346</v>
       </c>
@@ -28731,7 +28693,7 @@
         <v>8888</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>349</v>
       </c>
@@ -28763,7 +28725,7 @@
         <v>24704</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>352</v>
       </c>
@@ -28795,7 +28757,7 @@
         <v>21076</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>355</v>
       </c>
@@ -28827,7 +28789,7 @@
         <v>27036</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>358</v>
       </c>
@@ -28859,7 +28821,7 @@
         <v>164072</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>362</v>
       </c>
@@ -28891,7 +28853,7 @@
         <v>42516</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>365</v>
       </c>
@@ -28923,7 +28885,7 @@
         <v>145640</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>271</v>
       </c>
@@ -28955,7 +28917,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>458</v>
       </c>
@@ -28987,7 +28949,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>463</v>
       </c>
@@ -29019,7 +28981,7 @@
         <v>2892</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>181</v>
       </c>
@@ -29051,7 +29013,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>275</v>
       </c>
@@ -29083,7 +29045,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>279</v>
       </c>
@@ -29115,7 +29077,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>282</v>
       </c>
@@ -29147,7 +29109,7 @@
         <v>50604</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>285</v>
       </c>
@@ -29179,7 +29141,7 @@
         <v>21548</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>288</v>
       </c>
@@ -29211,7 +29173,7 @@
         <v>11936</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>368</v>
       </c>
@@ -29243,7 +29205,7 @@
         <v>23896</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>372</v>
       </c>
@@ -29275,7 +29237,7 @@
         <v>43768</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>375</v>
       </c>
@@ -29307,7 +29269,7 @@
         <v>191176</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>378</v>
       </c>
@@ -29339,7 +29301,7 @@
         <v>12628</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>381</v>
       </c>
@@ -29371,7 +29333,7 @@
         <v>63484</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>384</v>
       </c>
@@ -29403,7 +29365,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>387</v>
       </c>
@@ -29435,7 +29397,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>390</v>
       </c>
@@ -29465,7 +29427,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>393</v>
       </c>
@@ -29497,7 +29459,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>396</v>
       </c>
@@ -29529,7 +29491,7 @@
         <v>3596</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>479</v>
       </c>
@@ -29561,7 +29523,7 @@
         <v>18256</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>399</v>
       </c>
@@ -29593,7 +29555,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>292</v>
       </c>
@@ -29625,7 +29587,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>465</v>
       </c>
@@ -29657,7 +29619,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>470</v>
       </c>
@@ -29689,7 +29651,7 @@
         <v>20892</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>473</v>
       </c>
@@ -29721,7 +29683,7 @@
         <v>28024</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>476</v>
       </c>
@@ -29753,7 +29715,7 @@
         <v>121104</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>185</v>
       </c>
@@ -29785,7 +29747,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="116" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>189</v>
       </c>
@@ -29817,7 +29779,7 @@
         <v>158316</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>403</v>
       </c>
@@ -29849,7 +29811,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>224</v>
       </c>
@@ -29881,7 +29843,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>228</v>
       </c>
@@ -29913,7 +29875,7 @@
         <v>6552</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>231</v>
       </c>
@@ -29945,7 +29907,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>234</v>
       </c>
@@ -29977,7 +29939,7 @@
         <v>20720</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>237</v>
       </c>
@@ -30009,7 +29971,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>240</v>
       </c>
@@ -30041,7 +30003,7 @@
         <v>3516</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>243</v>
       </c>
@@ -30073,7 +30035,7 @@
         <v>59652</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>246</v>
       </c>
@@ -30105,7 +30067,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>295</v>
       </c>
@@ -30137,7 +30099,7 @@
         <v>6572</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>322</v>
       </c>
@@ -30169,7 +30131,7 @@
         <v>73144</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>326</v>
       </c>
@@ -30201,7 +30163,7 @@
         <v>6016</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>407</v>
       </c>
@@ -30233,7 +30195,7 @@
         <v>66764</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>411</v>
       </c>
@@ -30265,7 +30227,7 @@
         <v>3928</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>414</v>
       </c>
@@ -30297,7 +30259,7 @@
         <v>37528</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>417</v>
       </c>
@@ -30329,7 +30291,7 @@
         <v>77480</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>420</v>
       </c>
@@ -30361,7 +30323,7 @@
         <v>22252</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>423</v>
       </c>
@@ -30393,7 +30355,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>426</v>
       </c>
@@ -30425,7 +30387,7 @@
         <v>14000</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>429</v>
       </c>
@@ -30457,7 +30419,7 @@
         <v>150540</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>432</v>
       </c>
@@ -30489,7 +30451,7 @@
         <v>3432</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>435</v>
       </c>
@@ -30521,7 +30483,7 @@
         <v>145332</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>438</v>
       </c>
@@ -30553,7 +30515,7 @@
         <v>97836</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>441</v>
       </c>
@@ -30585,7 +30547,7 @@
         <v>20896</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>445</v>
       </c>
@@ -30617,7 +30579,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>448</v>
       </c>
@@ -30647,7 +30609,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>451</v>
       </c>
@@ -30679,7 +30641,7 @@
         <v>7356</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>454</v>
       </c>
@@ -30712,7 +30674,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J144" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:J144"/>
   <conditionalFormatting sqref="G2:G16">
     <cfRule type="cellIs" dxfId="28" priority="29" operator="lessThan">
       <formula>20000</formula>
@@ -30863,19 +30825,19 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{037935A5-1106-459B-9A86-1C0042E776B1}">
-  <dimension ref="A1:F49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" style="29" customWidth="1"/>
     <col min="2" max="2" width="32" style="29" customWidth="1"/>
-    <col min="3" max="3" width="78.140625" style="29" customWidth="1"/>
-    <col min="4" max="4" width="54.140625" style="29" customWidth="1"/>
+    <col min="3" max="3" width="78.1796875" style="29" customWidth="1"/>
+    <col min="4" max="4" width="54.1796875" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B1" s="30" t="s">
         <v>628</v>
@@ -30887,9 +30849,9 @@
         <v>630</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>484</v>
@@ -30901,9 +30863,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B3" s="29" t="s">
         <v>485</v>
@@ -30915,9 +30877,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B4" s="29" t="s">
         <v>487</v>
@@ -30929,9 +30891,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B5" s="29" t="s">
         <v>488</v>
@@ -30943,9 +30905,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B6" s="29" t="s">
         <v>490</v>
@@ -30957,9 +30919,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B7" s="29" t="s">
         <v>491</v>
@@ -30971,9 +30933,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" ht="40.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B8" s="29" t="s">
         <v>493</v>
@@ -30985,9 +30947,9 @@
         <v>632</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="29" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B9" s="29" t="s">
         <v>494</v>
@@ -30999,9 +30961,9 @@
         <v>640</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B10" s="29" t="s">
         <v>510</v>
@@ -31013,9 +30975,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B11" s="29" t="s">
         <v>511</v>
@@ -31027,9 +30989,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B12" s="29" t="s">
         <v>512</v>
@@ -31041,9 +31003,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B13" s="29" t="s">
         <v>513</v>
@@ -31055,9 +31017,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B14" s="29" t="s">
         <v>514</v>
@@ -31069,9 +31031,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="29" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B15" s="29" t="s">
         <v>515</v>
@@ -31083,9 +31045,9 @@
         <v>642</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B16" s="29" t="s">
         <v>518</v>
@@ -31097,9 +31059,9 @@
         <v>649</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B17" s="29" t="s">
         <v>519</v>
@@ -31111,9 +31073,9 @@
         <v>651</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B18" s="29" t="s">
         <v>520</v>
@@ -31125,9 +31087,9 @@
         <v>653</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B19" s="29" t="s">
         <v>521</v>
@@ -31138,368 +31100,363 @@
       <c r="D19" s="31" t="s">
         <v>653</v>
       </c>
-      <c r="F19" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B20" s="29" t="s">
         <v>522</v>
       </c>
       <c r="C20" s="31" t="s">
+        <v>655</v>
+      </c>
+      <c r="D20" s="29" t="s">
         <v>656</v>
       </c>
-      <c r="D20" s="29" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B21" s="29" t="s">
         <v>523</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D21" s="29" t="s">
-        <v>657</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B22" s="29" t="s">
         <v>524</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D22" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B23" s="29" t="s">
         <v>525</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D23" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B24" s="29" t="s">
         <v>526</v>
       </c>
       <c r="C24" s="29" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D24" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B25" s="29" t="s">
         <v>527</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D25" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B26" s="29" t="s">
         <v>528</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D26" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B27" s="29" t="s">
         <v>530</v>
       </c>
       <c r="C27" s="31" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D27" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A28" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B28" s="29" t="s">
         <v>532</v>
       </c>
       <c r="C28" s="31" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D28" s="29" t="s">
         <v>651</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="29" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B29" s="29" t="s">
         <v>534</v>
       </c>
       <c r="C29" s="31" t="s">
+        <v>665</v>
+      </c>
+      <c r="D29" s="29" t="s">
         <v>666</v>
       </c>
-      <c r="D29" s="29" t="s">
-        <v>667</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="43.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E29" s="29"/>
+    </row>
+    <row r="30" spans="1:5" ht="43.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B30" s="29" t="s">
         <v>569</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D30" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="34.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" ht="34.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B31" s="29" t="s">
         <v>570</v>
       </c>
       <c r="C31" s="31" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D31" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="28.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" ht="28.9" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B32" s="29" t="s">
         <v>571</v>
       </c>
       <c r="C32" s="31" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D32" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="33" spans="1:4" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B33" s="29" t="s">
         <v>572</v>
       </c>
       <c r="C33" s="29" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D33" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B34" s="29" t="s">
         <v>573</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D34" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B35" s="29" t="s">
         <v>574</v>
       </c>
       <c r="C35" s="31" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D35" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B36" s="29" t="s">
         <v>575</v>
       </c>
       <c r="C36" s="31" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D36" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B37" s="29" t="s">
         <v>576</v>
       </c>
       <c r="C37" s="31" t="s">
+        <v>674</v>
+      </c>
+      <c r="D37" s="31" t="s">
         <v>675</v>
       </c>
-      <c r="D37" s="31" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="60" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B38" s="29" t="s">
         <v>577</v>
       </c>
       <c r="C38" s="31" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D38" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="39" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B39" s="29" t="s">
         <v>578</v>
       </c>
       <c r="C39" s="31" t="s">
+        <v>674</v>
+      </c>
+      <c r="D39" s="31" t="s">
         <v>675</v>
       </c>
-      <c r="D39" s="31" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B40" s="29" t="s">
         <v>579</v>
       </c>
       <c r="C40" s="31" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D40" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="41" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B41" s="29" t="s">
         <v>580</v>
       </c>
       <c r="C41" s="31" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D41" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="42" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B42" s="29" t="s">
         <v>581</v>
       </c>
       <c r="C42" s="31" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D42" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="43" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B43" s="29" t="s">
         <v>582</v>
       </c>
       <c r="C43" s="31" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D43" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="44" spans="1:4" ht="45" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B44" s="29" t="s">
         <v>583</v>
       </c>
       <c r="C44" s="31" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D44" s="29" t="s">
         <v>649</v>
       </c>
     </row>
-    <row r="49" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D49" s="31"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D49" xr:uid="{037935A5-1106-459B-9A86-1C0042E776B1}"/>
+  <autoFilter ref="A1:D49"/>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -31507,179 +31464,179 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="243.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="243.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>683</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="36" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="36" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="36" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B10" r:id="rId1" display="https://doi.org/10.1080/13887890.2016.1259662" xr:uid="{CD274844-7B34-41CC-8E46-35C276933B0F}"/>
-    <hyperlink ref="B17" r:id="rId2" display="https://doi.org/10.5281/zenodo.3823337" xr:uid="{408A619D-6DF5-4402-B8BA-DFC1F2380E5E}"/>
-    <hyperlink ref="B6" r:id="rId3" display="https://doi.org/10.48156/1388.2023.1917025" xr:uid="{3049B77C-7C28-4397-86AE-DCF76FE57561}"/>
-    <hyperlink ref="B3" r:id="rId4" display="https://doi.org/10.2779/462053" xr:uid="{99F41D28-C6F5-4711-856C-17DE9FBEC3D4}"/>
+    <hyperlink ref="B10" r:id="rId1" display="https://doi.org/10.1080/13887890.2016.1259662"/>
+    <hyperlink ref="B17" r:id="rId2" display="https://doi.org/10.5281/zenodo.3823337"/>
+    <hyperlink ref="B6" r:id="rId3" display="https://doi.org/10.48156/1388.2023.1917025"/>
+    <hyperlink ref="B3" r:id="rId4" display="https://doi.org/10.2779/462053"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>

--- a/data/20251212-OdonTraits_Europe.xlsx
+++ b/data/20251212-OdonTraits_Europe.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="6"/>
+    <workbookView xWindow="28680" yWindow="1680" windowWidth="29040" windowHeight="17520" firstSheet="1" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="taxonomic" sheetId="2" r:id="rId1"/>
@@ -30,7 +30,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">protection_endemism!$A$1:$G$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">taxonomic!$A$1:$E$144</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -11479,11 +11479,11 @@
         <v>68</v>
       </c>
       <c r="B22" s="8">
-        <f t="shared" ref="B22:C25" si="0">D22+F22</f>
+        <f>D22+F22</f>
         <v>28</v>
       </c>
       <c r="C22" s="8">
-        <f t="shared" si="0"/>
+        <f>E22+G22</f>
         <v>31</v>
       </c>
       <c r="D22" s="8">
@@ -11504,11 +11504,11 @@
         <v>73</v>
       </c>
       <c r="B23" s="8">
-        <f t="shared" si="0"/>
+        <f>D23+F23</f>
         <v>27</v>
       </c>
       <c r="C23" s="8">
-        <f t="shared" si="0"/>
+        <f>E23+G23</f>
         <v>38</v>
       </c>
       <c r="D23" s="8">
@@ -11529,11 +11529,11 @@
         <v>76</v>
       </c>
       <c r="B24" s="8">
-        <f t="shared" si="0"/>
+        <f>D24+F24</f>
         <v>23</v>
       </c>
       <c r="C24" s="8">
-        <f t="shared" si="0"/>
+        <f>E24+G24</f>
         <v>34</v>
       </c>
       <c r="D24" s="8">
@@ -11554,11 +11554,11 @@
         <v>79</v>
       </c>
       <c r="B25" s="8">
-        <f t="shared" si="0"/>
+        <f>D25+F25</f>
         <v>31</v>
       </c>
       <c r="C25" s="8">
-        <f t="shared" si="0"/>
+        <f>E25+G25</f>
         <v>36</v>
       </c>
       <c r="D25" s="8">
@@ -11602,11 +11602,11 @@
         <v>87</v>
       </c>
       <c r="B27" s="8">
-        <f t="shared" ref="B27:C32" si="1">D27+F27</f>
+        <f>D27+F27</f>
         <v>15</v>
       </c>
       <c r="C27" s="8">
-        <f t="shared" si="1"/>
+        <f>E27+G27</f>
         <v>19</v>
       </c>
       <c r="D27" s="8">
@@ -11627,11 +11627,11 @@
         <v>299</v>
       </c>
       <c r="B28" s="8">
-        <f t="shared" si="1"/>
+        <f>D28+F28</f>
         <v>23</v>
       </c>
       <c r="C28" s="8">
-        <f t="shared" si="1"/>
+        <f>E28+G28</f>
         <v>29</v>
       </c>
       <c r="D28" s="8">
@@ -11652,11 +11652,11 @@
         <v>304</v>
       </c>
       <c r="B29" s="8">
-        <f t="shared" si="1"/>
+        <f>D29+F29</f>
         <v>23</v>
       </c>
       <c r="C29" s="8">
-        <f t="shared" si="1"/>
+        <f>E29+G29</f>
         <v>29</v>
       </c>
       <c r="D29" s="8">
@@ -11677,11 +11677,11 @@
         <v>90</v>
       </c>
       <c r="B30" s="8">
-        <f t="shared" si="1"/>
+        <f>D30+F30</f>
         <v>19</v>
       </c>
       <c r="C30" s="8">
-        <f t="shared" si="1"/>
+        <f>E30+G30</f>
         <v>23</v>
       </c>
       <c r="D30" s="8">
@@ -11702,11 +11702,11 @@
         <v>94</v>
       </c>
       <c r="B31" s="8">
-        <f t="shared" si="1"/>
+        <f>D31+F31</f>
         <v>14</v>
       </c>
       <c r="C31" s="8">
-        <f t="shared" si="1"/>
+        <f>E31+G31</f>
         <v>18</v>
       </c>
       <c r="D31" s="8">
@@ -11727,11 +11727,11 @@
         <v>517</v>
       </c>
       <c r="B32" s="8">
-        <f t="shared" si="1"/>
+        <f>D32+F32</f>
         <v>14</v>
       </c>
       <c r="C32" s="8">
-        <f t="shared" si="1"/>
+        <f>E32+G32</f>
         <v>18</v>
       </c>
       <c r="D32" s="8">
@@ -11798,11 +11798,11 @@
         <v>106</v>
       </c>
       <c r="B35" s="8">
-        <f t="shared" ref="B35:B44" si="2">D35+F35</f>
+        <f>D35+F35</f>
         <v>20</v>
       </c>
       <c r="C35" s="8">
-        <f t="shared" ref="C35:C44" si="3">E35+G35</f>
+        <f>E35+G35</f>
         <v>23</v>
       </c>
       <c r="D35" s="8">
@@ -11823,11 +11823,11 @@
         <v>109</v>
       </c>
       <c r="B36" s="8">
-        <f t="shared" si="2"/>
+        <f>D36+F36</f>
         <v>21</v>
       </c>
       <c r="C36" s="8">
-        <f t="shared" si="3"/>
+        <f>E36+G36</f>
         <v>23</v>
       </c>
       <c r="D36" s="8">
@@ -11848,11 +11848,11 @@
         <v>112</v>
       </c>
       <c r="B37" s="8">
-        <f t="shared" si="2"/>
+        <f>D37+F37</f>
         <v>18</v>
       </c>
       <c r="C37" s="8">
-        <f t="shared" si="3"/>
+        <f>E37+G37</f>
         <v>21</v>
       </c>
       <c r="D37" s="8">
@@ -11873,11 +11873,11 @@
         <v>115</v>
       </c>
       <c r="B38" s="8">
-        <f t="shared" si="2"/>
+        <f>D38+F38</f>
         <v>13</v>
       </c>
       <c r="C38" s="8">
-        <f t="shared" si="3"/>
+        <f>E38+G38</f>
         <v>14.5</v>
       </c>
       <c r="D38" s="8">
@@ -11898,11 +11898,11 @@
         <v>118</v>
       </c>
       <c r="B39" s="8">
-        <f t="shared" si="2"/>
+        <f>D39+F39</f>
         <v>19</v>
       </c>
       <c r="C39" s="8">
-        <f t="shared" si="3"/>
+        <f>E39+G39</f>
         <v>25</v>
       </c>
       <c r="D39" s="8">
@@ -11923,11 +11923,11 @@
         <v>121</v>
       </c>
       <c r="B40" s="8">
-        <f t="shared" si="2"/>
+        <f>D40+F40</f>
         <v>14</v>
       </c>
       <c r="C40" s="8">
-        <f t="shared" si="3"/>
+        <f>E40+G40</f>
         <v>18</v>
       </c>
       <c r="D40" s="8">
@@ -11948,11 +11948,11 @@
         <v>124</v>
       </c>
       <c r="B41" s="8">
-        <f t="shared" si="2"/>
+        <f>D41+F41</f>
         <v>15</v>
       </c>
       <c r="C41" s="8">
-        <f t="shared" si="3"/>
+        <f>E41+G41</f>
         <v>19</v>
       </c>
       <c r="D41" s="8">
@@ -11973,11 +11973,11 @@
         <v>127</v>
       </c>
       <c r="B42" s="8">
-        <f t="shared" si="2"/>
+        <f>D42+F42</f>
         <v>17</v>
       </c>
       <c r="C42" s="8">
-        <f t="shared" si="3"/>
+        <f>E42+G42</f>
         <v>21</v>
       </c>
       <c r="D42" s="8">
@@ -11998,11 +11998,11 @@
         <v>130</v>
       </c>
       <c r="B43" s="8">
-        <f t="shared" si="2"/>
+        <f>D43+F43</f>
         <v>17</v>
       </c>
       <c r="C43" s="8">
-        <f t="shared" si="3"/>
+        <f>E43+G43</f>
         <v>20</v>
       </c>
       <c r="D43" s="8">
@@ -12023,11 +12023,11 @@
         <v>133</v>
       </c>
       <c r="B44" s="8">
-        <f t="shared" si="2"/>
+        <f>D44+F44</f>
         <v>14</v>
       </c>
       <c r="C44" s="8">
-        <f t="shared" si="3"/>
+        <f>E44+G44</f>
         <v>21</v>
       </c>
       <c r="D44" s="8">
@@ -12351,11 +12351,11 @@
         <v>140</v>
       </c>
       <c r="B58" s="8">
-        <f t="shared" ref="B58:C60" si="4">D58+F58</f>
+        <f>D58+F58</f>
         <v>18</v>
       </c>
       <c r="C58" s="8">
-        <f t="shared" si="4"/>
+        <f>E58+G58</f>
         <v>22</v>
       </c>
       <c r="D58" s="8">
@@ -12376,11 +12376,11 @@
         <v>144</v>
       </c>
       <c r="B59" s="8">
-        <f t="shared" si="4"/>
+        <f>D59+F59</f>
         <v>25</v>
       </c>
       <c r="C59" s="8">
-        <f t="shared" si="4"/>
+        <f>E59+G59</f>
         <v>31</v>
       </c>
       <c r="D59" s="8">
@@ -12401,11 +12401,11 @@
         <v>147</v>
       </c>
       <c r="B60" s="8">
-        <f t="shared" si="4"/>
+        <f>D60+F60</f>
         <v>17</v>
       </c>
       <c r="C60" s="8">
-        <f t="shared" si="4"/>
+        <f>E60+G60</f>
         <v>20</v>
       </c>
       <c r="D60" s="8">
@@ -12564,11 +12564,11 @@
         <v>154</v>
       </c>
       <c r="B67" s="8">
-        <f t="shared" ref="B67:C70" si="5">D67+F67</f>
+        <f>D67+F67</f>
         <v>18</v>
       </c>
       <c r="C67" s="8">
-        <f t="shared" si="5"/>
+        <f>E67+G67</f>
         <v>21</v>
       </c>
       <c r="D67" s="8">
@@ -12589,11 +12589,11 @@
         <v>157</v>
       </c>
       <c r="B68" s="8">
-        <f t="shared" si="5"/>
+        <f>D68+F68</f>
         <v>17</v>
       </c>
       <c r="C68" s="8">
-        <f t="shared" si="5"/>
+        <f>E68+G68</f>
         <v>21</v>
       </c>
       <c r="D68" s="8">
@@ -12614,11 +12614,11 @@
         <v>160</v>
       </c>
       <c r="B69" s="8">
-        <f t="shared" si="5"/>
+        <f>D69+F69</f>
         <v>16</v>
       </c>
       <c r="C69" s="8">
-        <f t="shared" si="5"/>
+        <f>E69+G69</f>
         <v>21</v>
       </c>
       <c r="D69" s="8">
@@ -12639,11 +12639,11 @@
         <v>163</v>
       </c>
       <c r="B70" s="8">
-        <f t="shared" si="5"/>
+        <f>D70+F70</f>
         <v>16</v>
       </c>
       <c r="C70" s="8">
-        <f t="shared" si="5"/>
+        <f>E70+G70</f>
         <v>19</v>
       </c>
       <c r="D70" s="8">
@@ -12781,11 +12781,11 @@
         <v>306</v>
       </c>
       <c r="B76" s="8">
-        <f t="shared" ref="B76:C80" si="6">D76+F76</f>
+        <f>D76+F76</f>
         <v>23</v>
       </c>
       <c r="C76" s="8">
-        <f t="shared" si="6"/>
+        <f>E76+G76</f>
         <v>26</v>
       </c>
       <c r="D76" s="8">
@@ -12806,11 +12806,11 @@
         <v>310</v>
       </c>
       <c r="B77" s="8">
-        <f t="shared" si="6"/>
+        <f>D77+F77</f>
         <v>24</v>
       </c>
       <c r="C77" s="8">
-        <f t="shared" si="6"/>
+        <f>E77+G77</f>
         <v>35</v>
       </c>
       <c r="D77" s="8">
@@ -12831,11 +12831,11 @@
         <v>313</v>
       </c>
       <c r="B78" s="8">
-        <f t="shared" si="6"/>
+        <f>D78+F78</f>
         <v>22</v>
       </c>
       <c r="C78" s="8">
-        <f t="shared" si="6"/>
+        <f>E78+G78</f>
         <v>29</v>
       </c>
       <c r="D78" s="8">
@@ -12856,11 +12856,11 @@
         <v>316</v>
       </c>
       <c r="B79" s="8">
-        <f t="shared" si="6"/>
+        <f>D79+F79</f>
         <v>24</v>
       </c>
       <c r="C79" s="8">
-        <f t="shared" si="6"/>
+        <f>E79+G79</f>
         <v>31</v>
       </c>
       <c r="D79" s="8">
@@ -12881,11 +12881,11 @@
         <v>319</v>
       </c>
       <c r="B80" s="8">
-        <f t="shared" si="6"/>
+        <f>D80+F80</f>
         <v>22</v>
       </c>
       <c r="C80" s="8">
-        <f t="shared" si="6"/>
+        <f>E80+G80</f>
         <v>26</v>
       </c>
       <c r="D80" s="8">
@@ -13598,11 +13598,11 @@
         <v>465</v>
       </c>
       <c r="B111" s="8">
-        <f t="shared" ref="B111:C113" si="7">D111+F111</f>
+        <f>D111+F111</f>
         <v>18</v>
       </c>
       <c r="C111" s="8">
-        <f t="shared" si="7"/>
+        <f>E111+G111</f>
         <v>22</v>
       </c>
       <c r="D111" s="8">
@@ -13623,11 +13623,11 @@
         <v>470</v>
       </c>
       <c r="B112" s="8">
-        <f t="shared" si="7"/>
+        <f>D112+F112</f>
         <v>16</v>
       </c>
       <c r="C112" s="8">
-        <f t="shared" si="7"/>
+        <f>E112+G112</f>
         <v>19</v>
       </c>
       <c r="D112" s="8">
@@ -13648,11 +13648,11 @@
         <v>473</v>
       </c>
       <c r="B113" s="8">
-        <f t="shared" si="7"/>
+        <f>D113+F113</f>
         <v>18</v>
       </c>
       <c r="C113" s="8">
-        <f t="shared" si="7"/>
+        <f>E113+G113</f>
         <v>24</v>
       </c>
       <c r="D113" s="8">
